--- a/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
+++ b/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -70,6 +70,11 @@
     </font>
     <font>
       <name val="游ゴシック"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="メイリオ"/>
       <b val="1"/>
       <sz val="10"/>
     </font>
@@ -207,7 +212,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -307,6 +312,8 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -673,7 +680,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -782,82 +789,129 @@
       <c r="E9" s="21" t="n"/>
       <c r="F9" s="22" t="n"/>
     </row>
-    <row r="10" ht="8" customHeight="1"/>
+    <row r="10" ht="8" customHeight="1">
+      <c r="A10" s="37" t="inlineStr">
+        <is>
+          <t>■ 対応サマリー</t>
+        </is>
+      </c>
+    </row>
     <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="38" t="inlineStr">
+        <is>
+          <t>採用方針</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="28" customHeight="1">
+      <c r="A12" s="38" t="inlineStr">
+        <is>
+          <t>主要変更</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="38" t="inlineStr">
+        <is>
+          <t>テスト結果</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="38" t="inlineStr">
+        <is>
+          <t>リリース状況</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="38" t="inlineStr">
+        <is>
+          <t>ロールバック手順</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>■ 対応経緯タイムライン</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="7" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B18" s="7" t="inlineStr">
         <is>
           <t>日時</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C18" s="7" t="inlineStr">
         <is>
           <t>発生元</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D18" s="7" t="inlineStr">
         <is>
           <t>フェーズ</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E18" s="7" t="inlineStr">
         <is>
           <t>内容・決定事項</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F18" s="7" t="inlineStr">
         <is>
           <t>変更・判断の理由</t>
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="15" t="n"/>
-      <c r="B13" s="15" t="n"/>
-      <c r="C13" s="15" t="n"/>
-      <c r="D13" s="15" t="n"/>
-      <c r="E13" s="15" t="n"/>
-      <c r="F13" s="15" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="15" t="n"/>
-      <c r="B14" s="15" t="n"/>
-      <c r="C14" s="15" t="n"/>
-      <c r="D14" s="15" t="n"/>
-      <c r="E14" s="15" t="n"/>
-      <c r="F14" s="15" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="15" t="n"/>
-      <c r="B15" s="15" t="n"/>
-      <c r="C15" s="15" t="n"/>
-      <c r="D15" s="15" t="n"/>
-      <c r="E15" s="15" t="n"/>
-      <c r="F15" s="15" t="n"/>
+    <row r="19">
+      <c r="A19" s="15" t="n"/>
+      <c r="B19" s="15" t="n"/>
+      <c r="C19" s="15" t="n"/>
+      <c r="D19" s="15" t="n"/>
+      <c r="E19" s="15" t="n"/>
+      <c r="F19" s="15" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="n"/>
+      <c r="B20" s="15" t="n"/>
+      <c r="C20" s="15" t="n"/>
+      <c r="D20" s="15" t="n"/>
+      <c r="E20" s="15" t="n"/>
+      <c r="F20" s="15" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="n"/>
+      <c r="B21" s="15" t="n"/>
+      <c r="C21" s="15" t="n"/>
+      <c r="D21" s="15" t="n"/>
+      <c r="E21" s="15" t="n"/>
+      <c r="F21" s="15" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="10">
+  <mergeCells count="16">
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A11:F11"/>
+    <mergeCell ref="B12:F12"/>
     <mergeCell ref="B7:F7"/>
+    <mergeCell ref="A10:F10"/>
     <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B15:F15"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B11:F11"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B14:F14"/>
+    <mergeCell ref="A17:F17"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="B9:F9"/>
+    <mergeCell ref="B13:F13"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9"/>

--- a/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
+++ b/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
@@ -907,8 +907,8 @@
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="B3:F3"/>
     <mergeCell ref="B5:F5"/>
+    <mergeCell ref="A17:F17"/>
     <mergeCell ref="B14:F14"/>
-    <mergeCell ref="A17:F17"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="B13:F13"/>
@@ -1319,7 +1319,7 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>名前</t>
+          <t>対象</t>
         </is>
       </c>
       <c r="C28" s="7" t="inlineStr">
@@ -1786,7 +1786,7 @@
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>API名</t>
+          <t>対象</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">

--- a/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
+++ b/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
@@ -212,7 +212,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -314,6 +314,18 @@
     </xf>
     <xf numFmtId="0" fontId="9" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -680,7 +692,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -789,128 +801,197 @@
       <c r="E9" s="21" t="n"/>
       <c r="F9" s="22" t="n"/>
     </row>
-    <row r="10" ht="8" customHeight="1">
-      <c r="A10" s="37" t="inlineStr">
+    <row r="10" ht="28" customHeight="1">
+      <c r="A10" s="39" t="inlineStr">
         <is>
           <t>■ 対応サマリー</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="38" t="inlineStr">
+    <row r="11" ht="40" customHeight="1">
+      <c r="A11" s="40" t="inlineStr">
         <is>
           <t>採用方針</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="28" customHeight="1">
-      <c r="A12" s="38" t="inlineStr">
+      <c r="B11" s="41" t="n"/>
+    </row>
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="40" t="inlineStr">
         <is>
           <t>主要変更</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="38" t="inlineStr">
-        <is>
-          <t>テスト結果</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="38" t="inlineStr">
-        <is>
-          <t>リリース状況</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="38" t="inlineStr">
+      <c r="B12" s="41" t="n"/>
+    </row>
+    <row r="13" ht="40" customHeight="1">
+      <c r="A13" s="40" t="inlineStr">
+        <is>
+          <t>修正前（現状）</t>
+        </is>
+      </c>
+      <c r="B13" s="41" t="n"/>
+    </row>
+    <row r="14" ht="40" customHeight="1">
+      <c r="A14" s="40" t="inlineStr">
+        <is>
+          <t>修正後（期待挙動）</t>
+        </is>
+      </c>
+      <c r="B14" s="41" t="n"/>
+    </row>
+    <row r="15" ht="40" customHeight="1">
+      <c r="A15" s="40" t="inlineStr">
         <is>
           <t>ロールバック手順</t>
         </is>
       </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+      <c r="B15" s="41" t="n"/>
+    </row>
+    <row r="17" ht="28" customHeight="1">
+      <c r="A17" s="42" t="inlineStr">
+        <is>
+          <t>■ 判断保留事項</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="43" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B18" s="43" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C18" s="43" t="inlineStr">
+        <is>
+          <t>影響範囲</t>
+        </is>
+      </c>
+      <c r="D18" s="43" t="inlineStr">
+        <is>
+          <t>期待する判断者</t>
+        </is>
+      </c>
+      <c r="E18" s="43" t="inlineStr">
+        <is>
+          <t>関連ファイル</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="44" t="n"/>
+      <c r="B19" s="44" t="n"/>
+      <c r="C19" s="44" t="n"/>
+      <c r="D19" s="44" t="n"/>
+      <c r="E19" s="44" t="n"/>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="44" t="n"/>
+      <c r="B20" s="44" t="n"/>
+      <c r="C20" s="44" t="n"/>
+      <c r="D20" s="44" t="n"/>
+      <c r="E20" s="44" t="n"/>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="44" t="n"/>
+      <c r="B21" s="44" t="n"/>
+      <c r="C21" s="44" t="n"/>
+      <c r="D21" s="44" t="n"/>
+      <c r="E21" s="44" t="n"/>
+    </row>
+    <row r="22" ht="8" customHeight="1"/>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>■ 対応経緯タイムライン</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B24" s="7" t="inlineStr">
         <is>
           <t>日時</t>
         </is>
       </c>
-      <c r="C18" s="7" t="inlineStr">
+      <c r="C24" s="7" t="inlineStr">
         <is>
           <t>発生元</t>
         </is>
       </c>
-      <c r="D18" s="7" t="inlineStr">
+      <c r="D24" s="7" t="inlineStr">
         <is>
           <t>フェーズ</t>
         </is>
       </c>
-      <c r="E18" s="7" t="inlineStr">
+      <c r="E24" s="7" t="inlineStr">
         <is>
           <t>内容・決定事項</t>
         </is>
       </c>
-      <c r="F18" s="7" t="inlineStr">
+      <c r="F24" s="7" t="inlineStr">
         <is>
           <t>変更・判断の理由</t>
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="15" t="n"/>
-      <c r="B19" s="15" t="n"/>
-      <c r="C19" s="15" t="n"/>
-      <c r="D19" s="15" t="n"/>
-      <c r="E19" s="15" t="n"/>
-      <c r="F19" s="15" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="15" t="n"/>
-      <c r="B20" s="15" t="n"/>
-      <c r="C20" s="15" t="n"/>
-      <c r="D20" s="15" t="n"/>
-      <c r="E20" s="15" t="n"/>
-      <c r="F20" s="15" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="15" t="n"/>
-      <c r="B21" s="15" t="n"/>
-      <c r="C21" s="15" t="n"/>
-      <c r="D21" s="15" t="n"/>
-      <c r="E21" s="15" t="n"/>
-      <c r="F21" s="15" t="n"/>
-    </row>
+    <row r="25">
+      <c r="A25" s="15" t="n"/>
+      <c r="B25" s="15" t="n"/>
+      <c r="C25" s="15" t="n"/>
+      <c r="D25" s="15" t="n"/>
+      <c r="E25" s="15" t="n"/>
+      <c r="F25" s="15" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="15" t="n"/>
+      <c r="B26" s="15" t="n"/>
+      <c r="C26" s="15" t="n"/>
+      <c r="D26" s="15" t="n"/>
+      <c r="E26" s="15" t="n"/>
+      <c r="F26" s="15" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="15" t="n"/>
+      <c r="B27" s="15" t="n"/>
+      <c r="C27" s="15" t="n"/>
+      <c r="D27" s="15" t="n"/>
+      <c r="E27" s="15" t="n"/>
+      <c r="F27" s="15" t="n"/>
+    </row>
+    <row r="28"/>
+    <row r="29"/>
+    <row r="30"/>
+    <row r="31"/>
+    <row r="32"/>
+    <row r="33"/>
+    <row r="34"/>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="17">
     <mergeCell ref="B4:F4"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B9:F9"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="A10:F10"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B11:F11"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="A23:F23"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B8:F8"/>
-    <mergeCell ref="B9:F9"/>
     <mergeCell ref="B13:F13"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>

--- a/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
+++ b/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
@@ -142,7 +142,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -208,11 +208,26 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="45">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -324,6 +339,16 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -688,11 +713,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002E75B6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F34"/>
+  <dimension ref="A1:F27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -809,44 +833,64 @@
       </c>
     </row>
     <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="40" t="inlineStr">
+      <c r="A11" s="45" t="inlineStr">
         <is>
           <t>採用方針</t>
         </is>
       </c>
-      <c r="B11" s="41" t="n"/>
+      <c r="B11" s="46" t="n"/>
+      <c r="C11" s="47" t="n"/>
+      <c r="D11" s="47" t="n"/>
+      <c r="E11" s="47" t="n"/>
+      <c r="F11" s="48" t="n"/>
     </row>
     <row r="12" ht="40" customHeight="1">
-      <c r="A12" s="40" t="inlineStr">
+      <c r="A12" s="45" t="inlineStr">
         <is>
           <t>主要変更</t>
         </is>
       </c>
-      <c r="B12" s="41" t="n"/>
+      <c r="B12" s="46" t="n"/>
+      <c r="C12" s="47" t="n"/>
+      <c r="D12" s="47" t="n"/>
+      <c r="E12" s="47" t="n"/>
+      <c r="F12" s="48" t="n"/>
     </row>
     <row r="13" ht="40" customHeight="1">
-      <c r="A13" s="40" t="inlineStr">
+      <c r="A13" s="45" t="inlineStr">
         <is>
           <t>修正前（現状）</t>
         </is>
       </c>
-      <c r="B13" s="41" t="n"/>
+      <c r="B13" s="46" t="n"/>
+      <c r="C13" s="47" t="n"/>
+      <c r="D13" s="47" t="n"/>
+      <c r="E13" s="47" t="n"/>
+      <c r="F13" s="48" t="n"/>
     </row>
     <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="40" t="inlineStr">
+      <c r="A14" s="45" t="inlineStr">
         <is>
           <t>修正後（期待挙動）</t>
         </is>
       </c>
-      <c r="B14" s="41" t="n"/>
+      <c r="B14" s="46" t="n"/>
+      <c r="C14" s="47" t="n"/>
+      <c r="D14" s="47" t="n"/>
+      <c r="E14" s="47" t="n"/>
+      <c r="F14" s="48" t="n"/>
     </row>
     <row r="15" ht="40" customHeight="1">
-      <c r="A15" s="40" t="inlineStr">
+      <c r="A15" s="45" t="inlineStr">
         <is>
           <t>ロールバック手順</t>
         </is>
       </c>
-      <c r="B15" s="41" t="n"/>
+      <c r="B15" s="46" t="n"/>
+      <c r="C15" s="47" t="n"/>
+      <c r="D15" s="47" t="n"/>
+      <c r="E15" s="47" t="n"/>
+      <c r="F15" s="48" t="n"/>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="42" t="inlineStr">
@@ -856,52 +900,52 @@
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="43" t="inlineStr">
+      <c r="A18" s="49" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B18" s="43" t="inlineStr">
+      <c r="B18" s="49" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C18" s="43" t="inlineStr">
+      <c r="C18" s="49" t="inlineStr">
         <is>
           <t>影響範囲</t>
         </is>
       </c>
-      <c r="D18" s="43" t="inlineStr">
+      <c r="D18" s="49" t="inlineStr">
         <is>
           <t>期待する判断者</t>
         </is>
       </c>
-      <c r="E18" s="43" t="inlineStr">
+      <c r="E18" s="49" t="inlineStr">
         <is>
           <t>関連ファイル</t>
         </is>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="44" t="n"/>
-      <c r="B19" s="44" t="n"/>
-      <c r="C19" s="44" t="n"/>
-      <c r="D19" s="44" t="n"/>
-      <c r="E19" s="44" t="n"/>
+      <c r="A19" s="50" t="n"/>
+      <c r="B19" s="50" t="n"/>
+      <c r="C19" s="50" t="n"/>
+      <c r="D19" s="50" t="n"/>
+      <c r="E19" s="50" t="n"/>
     </row>
     <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="44" t="n"/>
-      <c r="B20" s="44" t="n"/>
-      <c r="C20" s="44" t="n"/>
-      <c r="D20" s="44" t="n"/>
-      <c r="E20" s="44" t="n"/>
+      <c r="A20" s="50" t="n"/>
+      <c r="B20" s="50" t="n"/>
+      <c r="C20" s="50" t="n"/>
+      <c r="D20" s="50" t="n"/>
+      <c r="E20" s="50" t="n"/>
     </row>
     <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="44" t="n"/>
-      <c r="B21" s="44" t="n"/>
-      <c r="C21" s="44" t="n"/>
-      <c r="D21" s="44" t="n"/>
-      <c r="E21" s="44" t="n"/>
+      <c r="A21" s="50" t="n"/>
+      <c r="B21" s="50" t="n"/>
+      <c r="C21" s="50" t="n"/>
+      <c r="D21" s="50" t="n"/>
+      <c r="E21" s="50" t="n"/>
     </row>
     <row r="22" ht="8" customHeight="1"/>
     <row r="23">
@@ -967,31 +1011,24 @@
       <c r="E27" s="15" t="n"/>
       <c r="F27" s="15" t="n"/>
     </row>
-    <row r="28"/>
-    <row r="29"/>
-    <row r="30"/>
-    <row r="31"/>
-    <row r="32"/>
-    <row r="33"/>
-    <row r="34"/>
   </sheetData>
   <mergeCells count="17">
     <mergeCell ref="B4:F4"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="B12:F12"/>
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B9:F9"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="B12:F12"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B3:F3"/>
     <mergeCell ref="A23:F23"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B9:F9"/>
     <mergeCell ref="B13:F13"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -1002,7 +1039,6 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002E75B6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1182,11 +1218,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002E75B6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D33"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1206,29 +1241,29 @@
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>■ 仮説検証テーブル</t>
+          <t>■ コード根拠テーブル</t>
         </is>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="7" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>ファイル名</t>
         </is>
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>仮説内容</t>
+          <t>行番号</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>備考</t>
+          <t>コード内容</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>判定</t>
+          <t>説明</t>
         </is>
       </c>
     </row>
@@ -1266,31 +1301,27 @@
     <row r="10" ht="28" customHeight="1">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>■ コード根拠テーブル</t>
+          <t>■ 影響範囲テーブル</t>
         </is>
       </c>
     </row>
     <row r="11" ht="28" customHeight="1">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>ファイル名</t>
+          <t>種別</t>
         </is>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>行番号</t>
+          <t>対象</t>
         </is>
       </c>
       <c r="C11" s="7" t="inlineStr">
         <is>
-          <t>コード内容</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="inlineStr">
-        <is>
-          <t>説明</t>
-        </is>
-      </c>
+          <t>役割</t>
+        </is>
+      </c>
+      <c r="D11" s="7" t="n"/>
     </row>
     <row r="12" ht="45" customHeight="1">
       <c r="A12" s="6" t="n"/>
@@ -1322,131 +1353,82 @@
       <c r="C16" s="6" t="n"/>
       <c r="D16" s="6" t="n"/>
     </row>
-    <row r="17" ht="8" customHeight="1"/>
-    <row r="18" ht="28" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>■ 影響範囲テーブル</t>
-        </is>
-      </c>
-    </row>
+    <row r="17" ht="8" customHeight="1">
+      <c r="A17" s="9" t="n"/>
+      <c r="B17" s="9" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="9" t="n"/>
+    </row>
+    <row r="18" ht="28" customHeight="1"/>
     <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="7" t="inlineStr">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>■ 関連コンポーネント一覧</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="40" customHeight="1">
+      <c r="A20" s="7" t="inlineStr">
         <is>
           <t>種別</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>対象</t>
         </is>
       </c>
-      <c r="C19" s="7" t="inlineStr">
+      <c r="C20" s="7" t="inlineStr">
         <is>
           <t>役割</t>
         </is>
       </c>
-      <c r="D19" s="7" t="n"/>
-    </row>
-    <row r="20" ht="40" customHeight="1">
-      <c r="A20" s="6" t="n"/>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="6" t="n"/>
+      <c r="D20" s="7" t="n"/>
     </row>
     <row r="21" ht="40" customHeight="1">
-      <c r="A21" s="9" t="n"/>
-      <c r="B21" s="9" t="n"/>
-      <c r="C21" s="9" t="n"/>
-      <c r="D21" s="9" t="n"/>
+      <c r="A21" s="6" t="n"/>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
     </row>
     <row r="22" ht="40" customHeight="1">
-      <c r="A22" s="6" t="n"/>
-      <c r="B22" s="6" t="n"/>
-      <c r="C22" s="6" t="n"/>
-      <c r="D22" s="6" t="n"/>
+      <c r="A22" s="9" t="n"/>
+      <c r="B22" s="9" t="n"/>
+      <c r="C22" s="9" t="n"/>
+      <c r="D22" s="9" t="n"/>
     </row>
     <row r="23" ht="40" customHeight="1">
-      <c r="A23" s="9" t="n"/>
-      <c r="B23" s="9" t="n"/>
-      <c r="C23" s="9" t="n"/>
-      <c r="D23" s="9" t="n"/>
+      <c r="A23" s="6" t="n"/>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n"/>
     </row>
     <row r="24" ht="40" customHeight="1">
-      <c r="A24" s="6" t="n"/>
-      <c r="B24" s="6" t="n"/>
-      <c r="C24" s="6" t="n"/>
-      <c r="D24" s="6" t="n"/>
+      <c r="A24" s="9" t="n"/>
+      <c r="B24" s="9" t="n"/>
+      <c r="C24" s="9" t="n"/>
+      <c r="D24" s="9" t="n"/>
     </row>
     <row r="25" ht="40" customHeight="1">
-      <c r="A25" s="9" t="n"/>
-      <c r="B25" s="9" t="n"/>
-      <c r="C25" s="9" t="n"/>
-      <c r="D25" s="9" t="n"/>
+      <c r="A25" s="6" t="n"/>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
     </row>
     <row r="26" ht="8" customHeight="1"/>
-    <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>■ 関連コンポーネント一覧</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="28" customHeight="1">
-      <c r="A28" s="7" t="inlineStr">
-        <is>
-          <t>種別</t>
-        </is>
-      </c>
-      <c r="B28" s="7" t="inlineStr">
-        <is>
-          <t>対象</t>
-        </is>
-      </c>
-      <c r="C28" s="7" t="inlineStr">
-        <is>
-          <t>役割</t>
-        </is>
-      </c>
-      <c r="D28" s="7" t="n"/>
-    </row>
-    <row r="29" ht="40" customHeight="1">
-      <c r="A29" s="6" t="n"/>
-      <c r="B29" s="6" t="n"/>
-      <c r="C29" s="6" t="n"/>
-      <c r="D29" s="6" t="n"/>
-    </row>
-    <row r="30" ht="40" customHeight="1">
-      <c r="A30" s="9" t="n"/>
-      <c r="B30" s="9" t="n"/>
-      <c r="C30" s="9" t="n"/>
-      <c r="D30" s="9" t="n"/>
-    </row>
-    <row r="31" ht="40" customHeight="1">
-      <c r="A31" s="6" t="n"/>
-      <c r="B31" s="6" t="n"/>
-      <c r="C31" s="6" t="n"/>
-      <c r="D31" s="6" t="n"/>
-    </row>
-    <row r="32" ht="40" customHeight="1">
-      <c r="A32" s="9" t="n"/>
-      <c r="B32" s="9" t="n"/>
-      <c r="C32" s="9" t="n"/>
-      <c r="D32" s="9" t="n"/>
-    </row>
-    <row r="33" ht="40" customHeight="1">
-      <c r="A33" s="6" t="n"/>
-      <c r="B33" s="6" t="n"/>
-      <c r="C33" s="6" t="n"/>
-      <c r="D33" s="6" t="n"/>
-    </row>
+    <row r="27" ht="28" customHeight="1"/>
+    <row r="28" ht="28" customHeight="1"/>
+    <row r="29" ht="40" customHeight="1"/>
+    <row r="30" ht="40" customHeight="1"/>
+    <row r="31" ht="40" customHeight="1"/>
+    <row r="32" ht="40" customHeight="1"/>
+    <row r="33" ht="40" customHeight="1"/>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A19:D19"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A10:D10"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9"/>
@@ -1456,7 +1438,6 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002E75B6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1659,7 +1640,6 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002E75B6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
@@ -1825,7 +1805,6 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <tabColor rgb="002E75B6"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>

--- a/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
+++ b/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
@@ -142,7 +142,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="16">
     <border>
       <left/>
       <right/>
@@ -223,11 +223,69 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4C6E7"/>
+      </bottom>
+    </border>
+    <border>
+      <right style="thin">
+        <color rgb="00B4C6E7"/>
+      </right>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4C6E7"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B4C6E7"/>
+      </left>
+      <top style="thin">
+        <color rgb="00B4C6E7"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00B4C6E7"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -349,6 +407,19 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -833,64 +904,64 @@
       </c>
     </row>
     <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="45" t="inlineStr">
+      <c r="A11" s="51" t="inlineStr">
         <is>
           <t>採用方針</t>
         </is>
       </c>
-      <c r="B11" s="46" t="n"/>
-      <c r="C11" s="47" t="n"/>
-      <c r="D11" s="47" t="n"/>
-      <c r="E11" s="47" t="n"/>
-      <c r="F11" s="48" t="n"/>
+      <c r="B11" s="52" t="n"/>
+      <c r="C11" s="53" t="n"/>
+      <c r="D11" s="53" t="n"/>
+      <c r="E11" s="53" t="n"/>
+      <c r="F11" s="54" t="n"/>
     </row>
     <row r="12" ht="40" customHeight="1">
-      <c r="A12" s="45" t="inlineStr">
+      <c r="A12" s="51" t="inlineStr">
         <is>
           <t>主要変更</t>
         </is>
       </c>
-      <c r="B12" s="46" t="n"/>
-      <c r="C12" s="47" t="n"/>
-      <c r="D12" s="47" t="n"/>
-      <c r="E12" s="47" t="n"/>
-      <c r="F12" s="48" t="n"/>
+      <c r="B12" s="52" t="n"/>
+      <c r="C12" s="53" t="n"/>
+      <c r="D12" s="53" t="n"/>
+      <c r="E12" s="53" t="n"/>
+      <c r="F12" s="54" t="n"/>
     </row>
     <row r="13" ht="40" customHeight="1">
-      <c r="A13" s="45" t="inlineStr">
+      <c r="A13" s="51" t="inlineStr">
         <is>
           <t>修正前（現状）</t>
         </is>
       </c>
-      <c r="B13" s="46" t="n"/>
-      <c r="C13" s="47" t="n"/>
-      <c r="D13" s="47" t="n"/>
-      <c r="E13" s="47" t="n"/>
-      <c r="F13" s="48" t="n"/>
+      <c r="B13" s="52" t="n"/>
+      <c r="C13" s="53" t="n"/>
+      <c r="D13" s="53" t="n"/>
+      <c r="E13" s="53" t="n"/>
+      <c r="F13" s="54" t="n"/>
     </row>
     <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="45" t="inlineStr">
+      <c r="A14" s="51" t="inlineStr">
         <is>
           <t>修正後（期待挙動）</t>
         </is>
       </c>
-      <c r="B14" s="46" t="n"/>
-      <c r="C14" s="47" t="n"/>
-      <c r="D14" s="47" t="n"/>
-      <c r="E14" s="47" t="n"/>
-      <c r="F14" s="48" t="n"/>
+      <c r="B14" s="52" t="n"/>
+      <c r="C14" s="53" t="n"/>
+      <c r="D14" s="53" t="n"/>
+      <c r="E14" s="53" t="n"/>
+      <c r="F14" s="54" t="n"/>
     </row>
     <row r="15" ht="40" customHeight="1">
-      <c r="A15" s="45" t="inlineStr">
+      <c r="A15" s="51" t="inlineStr">
         <is>
           <t>ロールバック手順</t>
         </is>
       </c>
-      <c r="B15" s="46" t="n"/>
-      <c r="C15" s="47" t="n"/>
-      <c r="D15" s="47" t="n"/>
-      <c r="E15" s="47" t="n"/>
-      <c r="F15" s="48" t="n"/>
+      <c r="B15" s="52" t="n"/>
+      <c r="C15" s="53" t="n"/>
+      <c r="D15" s="53" t="n"/>
+      <c r="E15" s="53" t="n"/>
+      <c r="F15" s="54" t="n"/>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="42" t="inlineStr">
@@ -900,52 +971,52 @@
       </c>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="49" t="inlineStr">
+      <c r="A18" s="55" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B18" s="49" t="inlineStr">
+      <c r="B18" s="56" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C18" s="49" t="inlineStr">
+      <c r="C18" s="54" t="n"/>
+      <c r="D18" s="56" t="inlineStr">
         <is>
           <t>影響範囲</t>
         </is>
       </c>
-      <c r="D18" s="49" t="inlineStr">
-        <is>
-          <t>期待する判断者</t>
-        </is>
-      </c>
-      <c r="E18" s="49" t="inlineStr">
+      <c r="E18" s="54" t="n"/>
+      <c r="F18" s="32" t="inlineStr">
         <is>
           <t>関連ファイル</t>
         </is>
       </c>
     </row>
     <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="50" t="n"/>
-      <c r="B19" s="50" t="n"/>
-      <c r="C19" s="50" t="n"/>
-      <c r="D19" s="50" t="n"/>
-      <c r="E19" s="50" t="n"/>
+      <c r="A19" s="24" t="n"/>
+      <c r="B19" s="57" t="n"/>
+      <c r="C19" s="54" t="n"/>
+      <c r="D19" s="57" t="n"/>
+      <c r="E19" s="54" t="n"/>
+      <c r="F19" s="32" t="n"/>
     </row>
     <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="50" t="n"/>
-      <c r="B20" s="50" t="n"/>
-      <c r="C20" s="50" t="n"/>
-      <c r="D20" s="50" t="n"/>
-      <c r="E20" s="50" t="n"/>
+      <c r="A20" s="24" t="n"/>
+      <c r="B20" s="57" t="n"/>
+      <c r="C20" s="54" t="n"/>
+      <c r="D20" s="57" t="n"/>
+      <c r="E20" s="54" t="n"/>
+      <c r="F20" s="32" t="n"/>
     </row>
     <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="50" t="n"/>
-      <c r="B21" s="50" t="n"/>
-      <c r="C21" s="50" t="n"/>
-      <c r="D21" s="50" t="n"/>
-      <c r="E21" s="50" t="n"/>
+      <c r="A21" s="24" t="n"/>
+      <c r="B21" s="57" t="n"/>
+      <c r="C21" s="54" t="n"/>
+      <c r="D21" s="57" t="n"/>
+      <c r="E21" s="54" t="n"/>
+      <c r="F21" s="32" t="n"/>
     </row>
     <row r="22" ht="8" customHeight="1"/>
     <row r="23">
@@ -1012,24 +1083,32 @@
       <c r="F27" s="15" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="17">
+  <mergeCells count="25">
     <mergeCell ref="B4:F4"/>
+    <mergeCell ref="D20:E20"/>
+    <mergeCell ref="B7:F7"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="D21:E21"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="B12:F12"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="B7:F7"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="B21:C21"/>
     <mergeCell ref="B11:F11"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B3:F3"/>
     <mergeCell ref="A23:F23"/>
-    <mergeCell ref="B5:F5"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B8:F8"/>
+    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D18:E18"/>
     <mergeCell ref="B9:F9"/>
-    <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B6:F6"/>
+    <mergeCell ref="B15:F15"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B5:F5"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9"/>

--- a/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
+++ b/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
@@ -910,10 +910,10 @@
         </is>
       </c>
       <c r="B11" s="52" t="n"/>
-      <c r="C11" s="53" t="n"/>
-      <c r="D11" s="53" t="n"/>
-      <c r="E11" s="53" t="n"/>
-      <c r="F11" s="54" t="n"/>
+      <c r="C11" s="21" t="n"/>
+      <c r="D11" s="21" t="n"/>
+      <c r="E11" s="21" t="n"/>
+      <c r="F11" s="22" t="n"/>
     </row>
     <row r="12" ht="40" customHeight="1">
       <c r="A12" s="51" t="inlineStr">
@@ -922,10 +922,10 @@
         </is>
       </c>
       <c r="B12" s="52" t="n"/>
-      <c r="C12" s="53" t="n"/>
-      <c r="D12" s="53" t="n"/>
-      <c r="E12" s="53" t="n"/>
-      <c r="F12" s="54" t="n"/>
+      <c r="C12" s="21" t="n"/>
+      <c r="D12" s="21" t="n"/>
+      <c r="E12" s="21" t="n"/>
+      <c r="F12" s="22" t="n"/>
     </row>
     <row r="13" ht="40" customHeight="1">
       <c r="A13" s="51" t="inlineStr">
@@ -934,10 +934,10 @@
         </is>
       </c>
       <c r="B13" s="52" t="n"/>
-      <c r="C13" s="53" t="n"/>
-      <c r="D13" s="53" t="n"/>
-      <c r="E13" s="53" t="n"/>
-      <c r="F13" s="54" t="n"/>
+      <c r="C13" s="21" t="n"/>
+      <c r="D13" s="21" t="n"/>
+      <c r="E13" s="21" t="n"/>
+      <c r="F13" s="22" t="n"/>
     </row>
     <row r="14" ht="40" customHeight="1">
       <c r="A14" s="51" t="inlineStr">
@@ -946,10 +946,10 @@
         </is>
       </c>
       <c r="B14" s="52" t="n"/>
-      <c r="C14" s="53" t="n"/>
-      <c r="D14" s="53" t="n"/>
-      <c r="E14" s="53" t="n"/>
-      <c r="F14" s="54" t="n"/>
+      <c r="C14" s="21" t="n"/>
+      <c r="D14" s="21" t="n"/>
+      <c r="E14" s="21" t="n"/>
+      <c r="F14" s="22" t="n"/>
     </row>
     <row r="15" ht="40" customHeight="1">
       <c r="A15" s="51" t="inlineStr">
@@ -958,10 +958,10 @@
         </is>
       </c>
       <c r="B15" s="52" t="n"/>
-      <c r="C15" s="53" t="n"/>
-      <c r="D15" s="53" t="n"/>
-      <c r="E15" s="53" t="n"/>
-      <c r="F15" s="54" t="n"/>
+      <c r="C15" s="21" t="n"/>
+      <c r="D15" s="21" t="n"/>
+      <c r="E15" s="21" t="n"/>
+      <c r="F15" s="22" t="n"/>
     </row>
     <row r="17" ht="28" customHeight="1">
       <c r="A17" s="42" t="inlineStr">
@@ -981,14 +981,14 @@
           <t>内容</t>
         </is>
       </c>
-      <c r="C18" s="54" t="n"/>
-      <c r="D18" s="56" t="inlineStr">
+      <c r="C18" s="53" t="n"/>
+      <c r="D18" s="54" t="n"/>
+      <c r="E18" s="32" t="inlineStr">
         <is>
           <t>影響範囲</t>
         </is>
       </c>
-      <c r="E18" s="54" t="n"/>
-      <c r="F18" s="32" t="inlineStr">
+      <c r="F18" s="55" t="inlineStr">
         <is>
           <t>関連ファイル</t>
         </is>
@@ -997,26 +997,26 @@
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="24" t="n"/>
       <c r="B19" s="57" t="n"/>
-      <c r="C19" s="54" t="n"/>
-      <c r="D19" s="57" t="n"/>
-      <c r="E19" s="54" t="n"/>
-      <c r="F19" s="32" t="n"/>
+      <c r="C19" s="53" t="n"/>
+      <c r="D19" s="54" t="n"/>
+      <c r="E19" s="32" t="n"/>
+      <c r="F19" s="24" t="n"/>
     </row>
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="24" t="n"/>
       <c r="B20" s="57" t="n"/>
-      <c r="C20" s="54" t="n"/>
-      <c r="D20" s="57" t="n"/>
-      <c r="E20" s="54" t="n"/>
-      <c r="F20" s="32" t="n"/>
+      <c r="C20" s="53" t="n"/>
+      <c r="D20" s="54" t="n"/>
+      <c r="E20" s="32" t="n"/>
+      <c r="F20" s="24" t="n"/>
     </row>
     <row r="21" ht="28" customHeight="1">
       <c r="A21" s="24" t="n"/>
       <c r="B21" s="57" t="n"/>
-      <c r="C21" s="54" t="n"/>
-      <c r="D21" s="57" t="n"/>
-      <c r="E21" s="54" t="n"/>
-      <c r="F21" s="32" t="n"/>
+      <c r="C21" s="53" t="n"/>
+      <c r="D21" s="54" t="n"/>
+      <c r="E21" s="32" t="n"/>
+      <c r="F21" s="24" t="n"/>
     </row>
     <row r="22" ht="8" customHeight="1"/>
     <row r="23">
@@ -1083,32 +1083,28 @@
       <c r="F27" s="15" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="25">
+  <mergeCells count="21">
     <mergeCell ref="B4:F4"/>
-    <mergeCell ref="D20:E20"/>
     <mergeCell ref="B7:F7"/>
-    <mergeCell ref="D19:E19"/>
     <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="D21:E21"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B19:D19"/>
     <mergeCell ref="B11:F11"/>
     <mergeCell ref="A23:F23"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="B14:F14"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="B13:F13"/>
+    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A10:F10"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D18:E18"/>
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B15:F15"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B20:C20"/>
     <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B18:D18"/>
+    <mergeCell ref="B21:D21"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9"/>

--- a/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
+++ b/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
@@ -976,14 +976,14 @@
           <t>No</t>
         </is>
       </c>
-      <c r="B18" s="56" t="inlineStr">
+      <c r="B18" s="55" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="C18" s="53" t="n"/>
-      <c r="D18" s="54" t="n"/>
-      <c r="E18" s="32" t="inlineStr">
+      <c r="C18" s="21" t="n"/>
+      <c r="D18" s="22" t="n"/>
+      <c r="E18" s="55" t="inlineStr">
         <is>
           <t>影響範囲</t>
         </is>
@@ -996,26 +996,26 @@
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="24" t="n"/>
-      <c r="B19" s="57" t="n"/>
-      <c r="C19" s="53" t="n"/>
-      <c r="D19" s="54" t="n"/>
-      <c r="E19" s="32" t="n"/>
+      <c r="B19" s="24" t="n"/>
+      <c r="C19" s="21" t="n"/>
+      <c r="D19" s="22" t="n"/>
+      <c r="E19" s="24" t="n"/>
       <c r="F19" s="24" t="n"/>
     </row>
     <row r="20" ht="28" customHeight="1">
       <c r="A20" s="24" t="n"/>
-      <c r="B20" s="57" t="n"/>
-      <c r="C20" s="53" t="n"/>
-      <c r="D20" s="54" t="n"/>
-      <c r="E20" s="32" t="n"/>
+      <c r="B20" s="24" t="n"/>
+      <c r="C20" s="21" t="n"/>
+      <c r="D20" s="22" t="n"/>
+      <c r="E20" s="24" t="n"/>
       <c r="F20" s="24" t="n"/>
     </row>
     <row r="21" ht="28" customHeight="1">
       <c r="A21" s="24" t="n"/>
-      <c r="B21" s="57" t="n"/>
-      <c r="C21" s="53" t="n"/>
-      <c r="D21" s="54" t="n"/>
-      <c r="E21" s="32" t="n"/>
+      <c r="B21" s="24" t="n"/>
+      <c r="C21" s="21" t="n"/>
+      <c r="D21" s="22" t="n"/>
+      <c r="E21" s="24" t="n"/>
       <c r="F21" s="24" t="n"/>
     </row>
     <row r="22" ht="8" customHeight="1"/>

--- a/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
+++ b/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
@@ -1336,11 +1336,7 @@
           <t>コード内容</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>説明</t>
-        </is>
-      </c>
+      <c r="D3" s="7" t="n"/>
     </row>
     <row r="4" ht="55" customHeight="1">
       <c r="A4" s="6" t="n"/>
@@ -1924,11 +1920,7 @@
           <t>対象</t>
         </is>
       </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>デプロイ方法</t>
-        </is>
-      </c>
+      <c r="D3" s="7" t="n"/>
     </row>
     <row r="4" ht="25" customHeight="1">
       <c r="A4" s="6" t="n"/>

--- a/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
+++ b/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
@@ -79,7 +79,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="15">
     <fill>
       <patternFill/>
     </fill>
@@ -139,6 +139,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00E2EFDA"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9E1F2"/>
+        <bgColor rgb="00D9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8EDF4"/>
+        <bgColor rgb="00E8EDF4"/>
       </patternFill>
     </fill>
   </fills>
@@ -285,7 +297,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -420,6 +432,18 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="5" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -787,7 +811,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -930,7 +954,7 @@
     <row r="13" ht="40" customHeight="1">
       <c r="A13" s="51" t="inlineStr">
         <is>
-          <t>修正前（現状）</t>
+          <t>ロールバック手順</t>
         </is>
       </c>
       <c r="B13" s="52" t="n"/>
@@ -939,60 +963,53 @@
       <c r="E13" s="21" t="n"/>
       <c r="F13" s="22" t="n"/>
     </row>
-    <row r="14" ht="40" customHeight="1">
-      <c r="A14" s="51" t="inlineStr">
-        <is>
-          <t>修正後（期待挙動）</t>
-        </is>
-      </c>
-      <c r="B14" s="52" t="n"/>
-      <c r="C14" s="21" t="n"/>
-      <c r="D14" s="21" t="n"/>
-      <c r="E14" s="21" t="n"/>
-      <c r="F14" s="22" t="n"/>
-    </row>
+    <row r="14" ht="40" customHeight="1"/>
     <row r="15" ht="40" customHeight="1">
-      <c r="A15" s="51" t="inlineStr">
-        <is>
-          <t>ロールバック手順</t>
-        </is>
-      </c>
-      <c r="B15" s="52" t="n"/>
-      <c r="C15" s="21" t="n"/>
-      <c r="D15" s="21" t="n"/>
-      <c r="E15" s="21" t="n"/>
-      <c r="F15" s="22" t="n"/>
+      <c r="A15" s="42" t="inlineStr">
+        <is>
+          <t>■ 判断保留事項</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="55" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B16" s="55" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C16" s="21" t="n"/>
+      <c r="D16" s="22" t="n"/>
+      <c r="E16" s="55" t="inlineStr">
+        <is>
+          <t>影響範囲</t>
+        </is>
+      </c>
+      <c r="F16" s="55" t="inlineStr">
+        <is>
+          <t>関連ファイル</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="28" customHeight="1">
-      <c r="A17" s="42" t="inlineStr">
-        <is>
-          <t>■ 判断保留事項</t>
-        </is>
-      </c>
+      <c r="A17" s="24" t="n"/>
+      <c r="B17" s="24" t="n"/>
+      <c r="C17" s="21" t="n"/>
+      <c r="D17" s="22" t="n"/>
+      <c r="E17" s="24" t="n"/>
+      <c r="F17" s="24" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="55" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B18" s="55" t="inlineStr">
-        <is>
-          <t>内容</t>
-        </is>
-      </c>
+      <c r="A18" s="24" t="n"/>
+      <c r="B18" s="24" t="n"/>
       <c r="C18" s="21" t="n"/>
       <c r="D18" s="22" t="n"/>
-      <c r="E18" s="55" t="inlineStr">
-        <is>
-          <t>影響範囲</t>
-        </is>
-      </c>
-      <c r="F18" s="55" t="inlineStr">
-        <is>
-          <t>関連ファイル</t>
-        </is>
-      </c>
+      <c r="E18" s="24" t="n"/>
+      <c r="F18" s="24" t="n"/>
     </row>
     <row r="19" ht="28" customHeight="1">
       <c r="A19" s="24" t="n"/>
@@ -1002,61 +1019,61 @@
       <c r="E19" s="24" t="n"/>
       <c r="F19" s="24" t="n"/>
     </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="24" t="n"/>
-      <c r="B20" s="24" t="n"/>
-      <c r="C20" s="21" t="n"/>
-      <c r="D20" s="22" t="n"/>
-      <c r="E20" s="24" t="n"/>
-      <c r="F20" s="24" t="n"/>
-    </row>
+    <row r="20" ht="28" customHeight="1"/>
     <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="24" t="n"/>
-      <c r="B21" s="24" t="n"/>
-      <c r="C21" s="21" t="n"/>
-      <c r="D21" s="22" t="n"/>
-      <c r="E21" s="24" t="n"/>
-      <c r="F21" s="24" t="n"/>
-    </row>
-    <row r="22" ht="8" customHeight="1"/>
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>■ 対応経緯タイムライン</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="8" customHeight="1">
+      <c r="A22" s="7" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>日時</t>
+        </is>
+      </c>
+      <c r="C22" s="7" t="inlineStr">
+        <is>
+          <t>発生元</t>
+        </is>
+      </c>
+      <c r="D22" s="7" t="inlineStr">
+        <is>
+          <t>フェーズ</t>
+        </is>
+      </c>
+      <c r="E22" s="7" t="inlineStr">
+        <is>
+          <t>内容・決定事項</t>
+        </is>
+      </c>
+      <c r="F22" s="7" t="inlineStr">
+        <is>
+          <t>変更・判断の理由</t>
+        </is>
+      </c>
+    </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>■ 対応経緯タイムライン</t>
-        </is>
-      </c>
+      <c r="A23" s="15" t="n"/>
+      <c r="B23" s="15" t="n"/>
+      <c r="C23" s="15" t="n"/>
+      <c r="D23" s="15" t="n"/>
+      <c r="E23" s="15" t="n"/>
+      <c r="F23" s="15" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="7" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B24" s="7" t="inlineStr">
-        <is>
-          <t>日時</t>
-        </is>
-      </c>
-      <c r="C24" s="7" t="inlineStr">
-        <is>
-          <t>発生元</t>
-        </is>
-      </c>
-      <c r="D24" s="7" t="inlineStr">
-        <is>
-          <t>フェーズ</t>
-        </is>
-      </c>
-      <c r="E24" s="7" t="inlineStr">
-        <is>
-          <t>内容・決定事項</t>
-        </is>
-      </c>
-      <c r="F24" s="7" t="inlineStr">
-        <is>
-          <t>変更・判断の理由</t>
-        </is>
-      </c>
+      <c r="A24" s="15" t="n"/>
+      <c r="B24" s="15" t="n"/>
+      <c r="C24" s="15" t="n"/>
+      <c r="D24" s="15" t="n"/>
+      <c r="E24" s="15" t="n"/>
+      <c r="F24" s="15" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="15" t="n"/>
@@ -1066,45 +1083,27 @@
       <c r="E25" s="15" t="n"/>
       <c r="F25" s="15" t="n"/>
     </row>
-    <row r="26">
-      <c r="A26" s="15" t="n"/>
-      <c r="B26" s="15" t="n"/>
-      <c r="C26" s="15" t="n"/>
-      <c r="D26" s="15" t="n"/>
-      <c r="E26" s="15" t="n"/>
-      <c r="F26" s="15" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="15" t="n"/>
-      <c r="B27" s="15" t="n"/>
-      <c r="C27" s="15" t="n"/>
-      <c r="D27" s="15" t="n"/>
-      <c r="E27" s="15" t="n"/>
-      <c r="F27" s="15" t="n"/>
-    </row>
   </sheetData>
-  <mergeCells count="21">
+  <mergeCells count="19">
     <mergeCell ref="B4:F4"/>
     <mergeCell ref="B7:F7"/>
     <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B17:D17"/>
+    <mergeCell ref="A21:F21"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="B12:F12"/>
     <mergeCell ref="B19:D19"/>
     <mergeCell ref="B11:F11"/>
-    <mergeCell ref="A23:F23"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="B14:F14"/>
     <mergeCell ref="B8:F8"/>
     <mergeCell ref="B13:F13"/>
-    <mergeCell ref="B20:D20"/>
     <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A15:F15"/>
+    <mergeCell ref="B16:D16"/>
     <mergeCell ref="B9:F9"/>
     <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B15:F15"/>
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="B5:F5"/>
     <mergeCell ref="B18:D18"/>
-    <mergeCell ref="B21:D21"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9"/>
@@ -1879,7 +1878,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D35"/>
+  <dimension ref="A1:D26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1938,164 +1937,136 @@
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>■ リリース前確認事項</t>
+          <t>■ デプロイ手順</t>
         </is>
       </c>
     </row>
     <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="7" t="n"/>
-      <c r="B8" s="7" t="inlineStr">
-        <is>
-          <t>確認内容</t>
-        </is>
-      </c>
-      <c r="C8" s="21" t="n"/>
-      <c r="D8" s="22" t="n"/>
+      <c r="A8" s="11" t="n"/>
     </row>
     <row r="9" ht="25" customHeight="1">
-      <c r="A9" s="35" t="n"/>
-      <c r="B9" s="36" t="n"/>
-      <c r="C9" s="35" t="inlineStr"/>
-      <c r="D9" s="36" t="inlineStr"/>
+      <c r="A9" s="11" t="n"/>
     </row>
     <row r="10" ht="25" customHeight="1">
-      <c r="A10" s="35" t="n"/>
-      <c r="B10" s="36" t="n"/>
-      <c r="C10" s="35" t="inlineStr"/>
-      <c r="D10" s="36" t="inlineStr"/>
+      <c r="A10" s="11" t="n"/>
     </row>
     <row r="11" ht="25" customHeight="1">
-      <c r="A11" s="35" t="n"/>
-      <c r="B11" s="36" t="n"/>
-      <c r="C11" s="35" t="inlineStr"/>
-      <c r="D11" s="36" t="inlineStr"/>
-    </row>
-    <row r="12" ht="25" customHeight="1">
-      <c r="A12" s="35" t="n"/>
-      <c r="B12" s="36" t="n"/>
-      <c r="C12" s="35" t="inlineStr"/>
-      <c r="D12" s="36" t="inlineStr"/>
-    </row>
-    <row r="13" ht="8" customHeight="1"/>
+      <c r="A11" s="11" t="n"/>
+    </row>
+    <row r="12" ht="25" customHeight="1"/>
+    <row r="13" ht="8" customHeight="1">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>■ 注意事項・リスク</t>
+        </is>
+      </c>
+    </row>
     <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>■ デプロイ手順</t>
-        </is>
-      </c>
+      <c r="A14" s="11" t="n"/>
     </row>
     <row r="15" ht="25" customHeight="1">
       <c r="A15" s="11" t="n"/>
     </row>
-    <row r="16" ht="25" customHeight="1">
-      <c r="A16" s="11" t="n"/>
-    </row>
+    <row r="16" ht="25" customHeight="1"/>
     <row r="17" ht="25" customHeight="1">
-      <c r="A17" s="11" t="n"/>
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>■ ロールバック手順</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="25" customHeight="1">
       <c r="A18" s="11" t="n"/>
     </row>
-    <row r="19" ht="8" customHeight="1"/>
+    <row r="19" ht="8" customHeight="1">
+      <c r="A19" s="20" t="n"/>
+    </row>
     <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>■ デプロイ後確認事項</t>
-        </is>
-      </c>
+      <c r="A20" s="11" t="n"/>
     </row>
     <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="7" t="n"/>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>確認内容</t>
-        </is>
-      </c>
-      <c r="C21" s="21" t="n"/>
-      <c r="D21" s="22" t="n"/>
-    </row>
-    <row r="22" ht="25" customHeight="1">
-      <c r="A22" s="35" t="n"/>
-      <c r="B22" s="36" t="n"/>
-      <c r="C22" s="35" t="inlineStr"/>
-      <c r="D22" s="36" t="inlineStr"/>
-    </row>
-    <row r="23" ht="25" customHeight="1">
-      <c r="A23" s="35" t="n"/>
-      <c r="B23" s="36" t="n"/>
-      <c r="C23" s="35" t="inlineStr"/>
-      <c r="D23" s="36" t="inlineStr"/>
-    </row>
-    <row r="24" ht="25" customHeight="1">
-      <c r="A24" s="35" t="n"/>
-      <c r="B24" s="36" t="n"/>
-      <c r="C24" s="35" t="inlineStr"/>
-      <c r="D24" s="36" t="inlineStr"/>
-    </row>
-    <row r="25" ht="25" customHeight="1">
-      <c r="A25" s="35" t="n"/>
-      <c r="B25" s="36" t="n"/>
-      <c r="C25" s="35" t="inlineStr"/>
-      <c r="D25" s="36" t="inlineStr"/>
-    </row>
-    <row r="26" ht="8" customHeight="1"/>
-    <row r="27" ht="28" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>■ 注意事項・リスク</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="35" customHeight="1">
-      <c r="A28" s="11" t="n"/>
-    </row>
-    <row r="29" ht="35" customHeight="1">
-      <c r="A29" s="11" t="n"/>
-    </row>
+      <c r="A21" s="11" t="n"/>
+    </row>
+    <row r="22" ht="6" customHeight="1"/>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="58" t="inlineStr">
+        <is>
+          <t>■ リリース実施記録</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="59" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B24" s="59" t="inlineStr">
+        <is>
+          <t>実施日時</t>
+        </is>
+      </c>
+      <c r="C24" s="59" t="inlineStr">
+        <is>
+          <t>対象環境</t>
+        </is>
+      </c>
+      <c r="D24" s="59" t="inlineStr">
+        <is>
+          <t>デプロイ結果</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="28" customHeight="1">
+      <c r="A25" s="61" t="inlineStr"/>
+      <c r="B25" s="61" t="inlineStr"/>
+      <c r="C25" s="61" t="inlineStr">
+        <is>
+          <t>ステージング</t>
+        </is>
+      </c>
+      <c r="D25" s="61" t="inlineStr"/>
+    </row>
+    <row r="26" ht="28" customHeight="1">
+      <c r="A26" s="61" t="inlineStr"/>
+      <c r="B26" s="61" t="inlineStr"/>
+      <c r="C26" s="61" t="inlineStr">
+        <is>
+          <t>本番</t>
+        </is>
+      </c>
+      <c r="D26" s="61" t="inlineStr"/>
+    </row>
+    <row r="27" ht="28" customHeight="1"/>
+    <row r="28" ht="35" customHeight="1"/>
+    <row r="29" ht="35" customHeight="1"/>
     <row r="30" ht="8" customHeight="1"/>
-    <row r="31" ht="28" customHeight="1">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>■ ロールバック手順</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="25" customHeight="1">
-      <c r="A32" s="11" t="n"/>
-    </row>
-    <row r="33" ht="25" customHeight="1">
-      <c r="A33" s="20" t="n"/>
-    </row>
-    <row r="34" ht="25" customHeight="1">
-      <c r="A34" s="11" t="n"/>
-    </row>
-    <row r="35" ht="25" customHeight="1">
-      <c r="A35" s="11" t="n"/>
-    </row>
+    <row r="31" ht="28" customHeight="1"/>
+    <row r="32" ht="25" customHeight="1"/>
+    <row r="33" ht="25" customHeight="1"/>
+    <row r="34" ht="25" customHeight="1"/>
+    <row r="35" ht="25" customHeight="1"/>
     <row r="36" ht="8" customHeight="1"/>
     <row r="37" ht="28" customHeight="1"/>
     <row r="38" ht="28" customHeight="1"/>
     <row r="39" ht="25" customHeight="1"/>
   </sheetData>
-  <mergeCells count="19">
+  <mergeCells count="16">
+    <mergeCell ref="A1:D1"/>
     <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A35:D35"/>
-    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A23:D23"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A18:D18"/>
     <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A29:D29"/>
-    <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="A34:D34"/>
+    <mergeCell ref="A21:D21"/>
     <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A1:D1"/>
     <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="B21:D21"/>
-    <mergeCell ref="A33:D33"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A13:D13"/>
     <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>

--- a/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
+++ b/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
@@ -1617,7 +1617,7 @@
     <row r="13" ht="28" customHeight="1">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>■ Before / After（実装後に記入）</t>
+          <t>■ Before / After</t>
         </is>
       </c>
     </row>

--- a/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
+++ b/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
@@ -1878,7 +1878,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1988,55 +1988,10 @@
       <c r="A21" s="11" t="n"/>
     </row>
     <row r="22" ht="6" customHeight="1"/>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="58" t="inlineStr">
-        <is>
-          <t>■ リリース実施記録</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="59" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B24" s="59" t="inlineStr">
-        <is>
-          <t>実施日時</t>
-        </is>
-      </c>
-      <c r="C24" s="59" t="inlineStr">
-        <is>
-          <t>対象環境</t>
-        </is>
-      </c>
-      <c r="D24" s="59" t="inlineStr">
-        <is>
-          <t>デプロイ結果</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="28" customHeight="1">
-      <c r="A25" s="61" t="inlineStr"/>
-      <c r="B25" s="61" t="inlineStr"/>
-      <c r="C25" s="61" t="inlineStr">
-        <is>
-          <t>ステージング</t>
-        </is>
-      </c>
-      <c r="D25" s="61" t="inlineStr"/>
-    </row>
-    <row r="26" ht="28" customHeight="1">
-      <c r="A26" s="61" t="inlineStr"/>
-      <c r="B26" s="61" t="inlineStr"/>
-      <c r="C26" s="61" t="inlineStr">
-        <is>
-          <t>本番</t>
-        </is>
-      </c>
-      <c r="D26" s="61" t="inlineStr"/>
-    </row>
+    <row r="23" ht="20" customHeight="1"/>
+    <row r="24" ht="18" customHeight="1"/>
+    <row r="25" ht="28" customHeight="1"/>
+    <row r="26" ht="28" customHeight="1"/>
     <row r="27" ht="28" customHeight="1"/>
     <row r="28" ht="35" customHeight="1"/>
     <row r="29" ht="35" customHeight="1"/>
@@ -2051,22 +2006,21 @@
     <row r="38" ht="28" customHeight="1"/>
     <row r="39" ht="25" customHeight="1"/>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="15">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="A18:D18"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A20:D20"/>
     <mergeCell ref="A21:D21"/>
     <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A2:D2"/>
     <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A13:D13"/>
     <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>

--- a/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
+++ b/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
@@ -1116,7 +1116,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1150,25 +1150,20 @@
       </c>
       <c r="B3" s="7" t="inlineStr">
         <is>
-          <t>方針名</t>
+          <t>概要</t>
         </is>
       </c>
       <c r="C3" s="7" t="inlineStr">
         <is>
-          <t>概要</t>
+          <t>メリット</t>
         </is>
       </c>
       <c r="D3" s="7" t="inlineStr">
         <is>
-          <t>メリット</t>
+          <t>デメリット</t>
         </is>
       </c>
       <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>デメリット</t>
-        </is>
-      </c>
-      <c r="F3" s="7" t="inlineStr">
         <is>
           <t>工数</t>
         </is>
@@ -1180,7 +1175,6 @@
       <c r="C4" s="6" t="n"/>
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
     </row>
     <row r="5" ht="80" customHeight="1">
       <c r="A5" s="9" t="n"/>
@@ -1188,7 +1182,6 @@
       <c r="C5" s="9" t="n"/>
       <c r="D5" s="9" t="n"/>
       <c r="E5" s="9" t="n"/>
-      <c r="F5" s="9" t="n"/>
     </row>
     <row r="6" ht="8" customHeight="1"/>
     <row r="7" ht="28" customHeight="1">
@@ -1211,40 +1204,32 @@
     </row>
     <row r="11">
       <c r="A11" s="7" t="n"/>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>確認内容</t>
-        </is>
-      </c>
+      <c r="B11" s="22" t="n"/>
       <c r="C11" s="21" t="n"/>
       <c r="D11" s="21" t="n"/>
-      <c r="E11" s="21" t="n"/>
-      <c r="F11" s="22" t="n"/>
+      <c r="E11" s="22" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="35" t="n"/>
-      <c r="B12" s="36" t="n"/>
-      <c r="C12" s="35" t="inlineStr"/>
-      <c r="D12" s="36" t="inlineStr"/>
+      <c r="B12" s="35" t="inlineStr"/>
+      <c r="C12" s="36" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="35" t="n"/>
-      <c r="B13" s="36" t="n"/>
-      <c r="C13" s="35" t="inlineStr"/>
-      <c r="D13" s="36" t="inlineStr"/>
+      <c r="B13" s="35" t="inlineStr"/>
+      <c r="C13" s="36" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="35" t="n"/>
-      <c r="B14" s="36" t="n"/>
-      <c r="C14" s="35" t="inlineStr"/>
-      <c r="D14" s="36" t="inlineStr"/>
+      <c r="B14" s="35" t="inlineStr"/>
+      <c r="C14" s="36" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="35" t="n"/>
-      <c r="B15" s="36" t="n"/>
-      <c r="C15" s="35" t="inlineStr"/>
-      <c r="D15" s="36" t="inlineStr"/>
-    </row>
+      <c r="B15" s="35" t="inlineStr"/>
+      <c r="C15" s="36" t="inlineStr"/>
+    </row>
+    <row r="16"/>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
@@ -1273,16 +1258,16 @@
     <row r="30" ht="35" customHeight="1"/>
   </sheetData>
   <mergeCells count="10">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A10:F10"/>
-    <mergeCell ref="A19:F19"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="B11:F11"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="A17:F17"/>
-    <mergeCell ref="A18:F18"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A7:F7"/>
+    <mergeCell ref="A20:E20"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A19:E19"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="B11:E11"/>
+    <mergeCell ref="A8:E8"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A18:E18"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9"/>
@@ -1878,7 +1863,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:D21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -2009,18 +1994,18 @@
   <mergeCells count="15">
     <mergeCell ref="A1:D1"/>
     <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A9:D9"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A15:D15"/>
     <mergeCell ref="A7:D7"/>
     <mergeCell ref="A19:D19"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A2:D2"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>

--- a/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
+++ b/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="対応方針" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="調査・影響範囲" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="対応内容" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="テスト・検証記録" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="リリース・ロールバック" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="テスト・検証" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="残対応・懸念・保留" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -77,6 +77,11 @@
       <name val="メイリオ"/>
       <b val="1"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <b val="1"/>
+      <sz val="12"/>
     </font>
   </fonts>
   <fills count="15">
@@ -297,7 +302,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="62">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -444,6 +449,15 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1119,11 +1133,11 @@
   <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="35" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="60" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="12" customWidth="1" min="7" max="7"/>
   </cols>
@@ -1229,7 +1243,6 @@
       <c r="B15" s="35" t="inlineStr"/>
       <c r="C15" s="36" t="inlineStr"/>
     </row>
-    <row r="16"/>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
@@ -1280,12 +1293,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="28" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
   </cols>
@@ -1300,27 +1313,31 @@
     <row r="2" ht="28" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>■ コード根拠テーブル</t>
+          <t>■ 影響範囲テーブル</t>
         </is>
       </c>
     </row>
     <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
-        <is>
-          <t>ファイル名</t>
-        </is>
-      </c>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>行番号</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>コード内容</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="n"/>
+      <c r="A3" s="62" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B3" s="62" t="inlineStr">
+        <is>
+          <t>種別</t>
+        </is>
+      </c>
+      <c r="C3" s="62" t="inlineStr">
+        <is>
+          <t>対象</t>
+        </is>
+      </c>
+      <c r="D3" s="62" t="inlineStr">
+        <is>
+          <t>問題ない根拠・対応内容</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="55" customHeight="1">
       <c r="A4" s="6" t="n"/>
@@ -1352,124 +1369,28 @@
       <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
     </row>
-    <row r="9" ht="8" customHeight="1"/>
-    <row r="10" ht="28" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>■ 影響範囲テーブル</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="28" customHeight="1">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>種別</t>
-        </is>
-      </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>対象</t>
-        </is>
-      </c>
-      <c r="C11" s="7" t="inlineStr">
-        <is>
-          <t>役割</t>
-        </is>
-      </c>
-      <c r="D11" s="7" t="n"/>
-    </row>
-    <row r="12" ht="45" customHeight="1">
-      <c r="A12" s="6" t="n"/>
-      <c r="B12" s="6" t="n"/>
-      <c r="C12" s="6" t="n"/>
-      <c r="D12" s="6" t="n"/>
-    </row>
-    <row r="13" ht="45" customHeight="1">
-      <c r="A13" s="9" t="n"/>
-      <c r="B13" s="9" t="n"/>
-      <c r="C13" s="9" t="n"/>
-      <c r="D13" s="9" t="n"/>
-    </row>
-    <row r="14" ht="45" customHeight="1">
-      <c r="A14" s="6" t="n"/>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="n"/>
-    </row>
-    <row r="15" ht="45" customHeight="1">
-      <c r="A15" s="9" t="n"/>
-      <c r="B15" s="9" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="9" t="n"/>
-    </row>
-    <row r="16" ht="45" customHeight="1">
-      <c r="A16" s="6" t="n"/>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="6" t="n"/>
-    </row>
-    <row r="17" ht="8" customHeight="1">
-      <c r="A17" s="9" t="n"/>
-      <c r="B17" s="9" t="n"/>
-      <c r="C17" s="9" t="n"/>
-      <c r="D17" s="9" t="n"/>
-    </row>
+    <row r="9" ht="8" customHeight="1">
+      <c r="A9" s="9" t="n"/>
+      <c r="B9" s="9" t="n"/>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="9" t="n"/>
+    </row>
+    <row r="10" ht="28" customHeight="1"/>
+    <row r="11" ht="28" customHeight="1"/>
+    <row r="12" ht="45" customHeight="1"/>
+    <row r="13" ht="45" customHeight="1"/>
+    <row r="14" ht="45" customHeight="1"/>
+    <row r="15" ht="45" customHeight="1"/>
+    <row r="16" ht="45" customHeight="1"/>
+    <row r="17" ht="8" customHeight="1"/>
     <row r="18" ht="28" customHeight="1"/>
-    <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>■ 関連コンポーネント一覧</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="40" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>種別</t>
-        </is>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
-        <is>
-          <t>対象</t>
-        </is>
-      </c>
-      <c r="C20" s="7" t="inlineStr">
-        <is>
-          <t>役割</t>
-        </is>
-      </c>
-      <c r="D20" s="7" t="n"/>
-    </row>
-    <row r="21" ht="40" customHeight="1">
-      <c r="A21" s="6" t="n"/>
-      <c r="B21" s="6" t="n"/>
-      <c r="C21" s="6" t="n"/>
-      <c r="D21" s="6" t="n"/>
-    </row>
-    <row r="22" ht="40" customHeight="1">
-      <c r="A22" s="9" t="n"/>
-      <c r="B22" s="9" t="n"/>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="9" t="n"/>
-    </row>
-    <row r="23" ht="40" customHeight="1">
-      <c r="A23" s="6" t="n"/>
-      <c r="B23" s="6" t="n"/>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="6" t="n"/>
-    </row>
-    <row r="24" ht="40" customHeight="1">
-      <c r="A24" s="9" t="n"/>
-      <c r="B24" s="9" t="n"/>
-      <c r="C24" s="9" t="n"/>
-      <c r="D24" s="9" t="n"/>
-    </row>
-    <row r="25" ht="40" customHeight="1">
-      <c r="A25" s="6" t="n"/>
-      <c r="B25" s="6" t="n"/>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="6" t="n"/>
-    </row>
+    <row r="19" ht="28" customHeight="1"/>
+    <row r="20" ht="40" customHeight="1"/>
+    <row r="21" ht="40" customHeight="1"/>
+    <row r="22" ht="40" customHeight="1"/>
+    <row r="23" ht="40" customHeight="1"/>
+    <row r="24" ht="40" customHeight="1"/>
+    <row r="25" ht="40" customHeight="1"/>
     <row r="26" ht="8" customHeight="1"/>
     <row r="27" ht="28" customHeight="1"/>
     <row r="28" ht="28" customHeight="1"/>
@@ -1479,12 +1400,6 @@
     <row r="32" ht="40" customHeight="1"/>
     <row r="33" ht="40" customHeight="1"/>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A2:D2"/>
-  </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9"/>
 </worksheet>
@@ -1496,7 +1411,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D26"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1513,158 +1428,157 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>■ バックアップ情報（修正前に記録）</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="3" t="inlineStr">
-        <is>
-          <t>Git hash（修正前）</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="n"/>
+    <row r="2" ht="24" customHeight="1">
+      <c r="A2" s="63" t="inlineStr">
+        <is>
+          <t>■ 対応内容（言語記述）</t>
+        </is>
+      </c>
+      <c r="B2" s="21" t="n"/>
+      <c r="C2" s="21" t="n"/>
+      <c r="D2" s="22" t="n"/>
+    </row>
+    <row r="3" ht="40" customHeight="1">
+      <c r="A3" s="29" t="inlineStr"/>
+      <c r="B3" s="21" t="n"/>
       <c r="C3" s="21" t="n"/>
       <c r="D3" s="22" t="n"/>
     </row>
-    <row r="4" ht="25" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>stash名</t>
-        </is>
-      </c>
-      <c r="B4" s="4" t="n"/>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" s="29" t="inlineStr"/>
+      <c r="B4" s="21" t="n"/>
       <c r="C4" s="21" t="n"/>
       <c r="D4" s="22" t="n"/>
     </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>巻き戻し方法</t>
-        </is>
-      </c>
-      <c r="B5" s="4" t="n"/>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" s="29" t="inlineStr"/>
+      <c r="B5" s="21" t="n"/>
       <c r="C5" s="21" t="n"/>
       <c r="D5" s="22" t="n"/>
     </row>
-    <row r="6" ht="8" customHeight="1"/>
+    <row r="6" ht="6" customHeight="1"/>
     <row r="7" ht="28" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
         <is>
+          <t>■ バックアップ情報（修正前に記録）</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="28" customHeight="1">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Git hash（修正前）</t>
+        </is>
+      </c>
+      <c r="B8" s="4" t="n"/>
+      <c r="C8" s="21" t="n"/>
+      <c r="D8" s="22" t="n"/>
+    </row>
+    <row r="9" ht="35" customHeight="1">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>stash名</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="21" t="n"/>
+      <c r="D9" s="22" t="n"/>
+    </row>
+    <row r="10" ht="35" customHeight="1">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>巻き戻し方法</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="21" t="n"/>
+      <c r="D10" s="22" t="n"/>
+    </row>
+    <row r="11" ht="35" customHeight="1"/>
+    <row r="12" ht="8" customHeight="1">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
           <t>■ 変更ファイル一覧</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="7" t="inlineStr">
+    <row r="13" ht="28" customHeight="1">
+      <c r="A13" s="7" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>ファイルパス</t>
         </is>
       </c>
-      <c r="C8" s="7" t="inlineStr">
+      <c r="C13" s="7" t="inlineStr">
         <is>
           <t>変更種別</t>
         </is>
       </c>
-      <c r="D8" s="7" t="inlineStr">
+      <c r="D13" s="7" t="inlineStr">
         <is>
           <t>変更概要</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="35" customHeight="1">
-      <c r="A9" s="6" t="n"/>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="6" t="n"/>
-    </row>
-    <row r="10" ht="35" customHeight="1">
-      <c r="A10" s="9" t="n"/>
-      <c r="B10" s="9" t="n"/>
-      <c r="C10" s="9" t="n"/>
-      <c r="D10" s="9" t="n"/>
-    </row>
-    <row r="11" ht="35" customHeight="1">
-      <c r="A11" s="6" t="n"/>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-    </row>
-    <row r="12" ht="8" customHeight="1"/>
-    <row r="13" ht="28" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="6" t="n"/>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+    </row>
+    <row r="15" ht="25" customHeight="1">
+      <c r="A15" s="9" t="n"/>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+    </row>
+    <row r="16" ht="25" customHeight="1">
+      <c r="A16" s="6" t="n"/>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+    </row>
+    <row r="17" ht="25" customHeight="1"/>
+    <row r="18" ht="8" customHeight="1">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>■ Before / After</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="18" t="n"/>
-    </row>
-    <row r="15" ht="25" customHeight="1">
-      <c r="A15" s="19" t="inlineStr"/>
-    </row>
-    <row r="16" ht="25" customHeight="1">
-      <c r="A16" s="19" t="inlineStr"/>
-    </row>
-    <row r="17" ht="25" customHeight="1">
-      <c r="A17" s="19" t="inlineStr"/>
-    </row>
-    <row r="18" ht="8" customHeight="1"/>
     <row r="19" ht="28" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="18" t="n"/>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="19" t="inlineStr"/>
+    </row>
+    <row r="21" ht="25" customHeight="1">
+      <c r="A21" s="19" t="inlineStr"/>
+    </row>
+    <row r="22" ht="25" customHeight="1">
+      <c r="A22" s="19" t="inlineStr"/>
+    </row>
+    <row r="23" ht="25" customHeight="1"/>
+    <row r="24" ht="25" customHeight="1">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>■ 影響確認チェックリスト</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="7" t="n"/>
-      <c r="B20" s="7" t="inlineStr">
+    <row r="25" ht="25" customHeight="1">
+      <c r="A25" s="7" t="n"/>
+      <c r="B25" s="7" t="inlineStr">
         <is>
           <t>確認内容</t>
         </is>
       </c>
-      <c r="C20" s="7" t="n"/>
-      <c r="D20" s="7" t="n"/>
-    </row>
-    <row r="21" ht="25" customHeight="1">
-      <c r="A21" s="35" t="n"/>
-      <c r="B21" s="36" t="n"/>
-      <c r="C21" s="35" t="inlineStr"/>
-      <c r="D21" s="36" t="inlineStr"/>
-    </row>
-    <row r="22" ht="25" customHeight="1">
-      <c r="A22" s="35" t="n"/>
-      <c r="B22" s="36" t="n"/>
-      <c r="C22" s="35" t="inlineStr"/>
-      <c r="D22" s="36" t="inlineStr"/>
-    </row>
-    <row r="23" ht="25" customHeight="1">
-      <c r="A23" s="35" t="n"/>
-      <c r="B23" s="36" t="n"/>
-      <c r="C23" s="35" t="inlineStr"/>
-      <c r="D23" s="36" t="inlineStr"/>
-    </row>
-    <row r="24" ht="25" customHeight="1">
-      <c r="A24" s="35" t="n"/>
-      <c r="B24" s="36" t="n"/>
-      <c r="C24" s="35" t="inlineStr"/>
-      <c r="D24" s="36" t="inlineStr"/>
-    </row>
-    <row r="25" ht="25" customHeight="1">
-      <c r="A25" s="35" t="n"/>
-      <c r="B25" s="36" t="n"/>
-      <c r="C25" s="35" t="inlineStr"/>
-      <c r="D25" s="36" t="inlineStr"/>
+      <c r="C25" s="7" t="n"/>
+      <c r="D25" s="7" t="n"/>
     </row>
     <row r="26" ht="25" customHeight="1">
       <c r="A26" s="35" t="n"/>
@@ -1672,20 +1586,54 @@
       <c r="C26" s="35" t="inlineStr"/>
       <c r="D26" s="36" t="inlineStr"/>
     </row>
+    <row r="27">
+      <c r="A27" s="35" t="n"/>
+      <c r="B27" s="36" t="n"/>
+      <c r="C27" s="35" t="inlineStr"/>
+      <c r="D27" s="36" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="35" t="n"/>
+      <c r="B28" s="36" t="n"/>
+      <c r="C28" s="35" t="inlineStr"/>
+      <c r="D28" s="36" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="35" t="n"/>
+      <c r="B29" s="36" t="n"/>
+      <c r="C29" s="35" t="inlineStr"/>
+      <c r="D29" s="36" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="35" t="n"/>
+      <c r="B30" s="36" t="n"/>
+      <c r="C30" s="35" t="inlineStr"/>
+      <c r="D30" s="36" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="35" t="n"/>
+      <c r="B31" s="36" t="n"/>
+      <c r="C31" s="35" t="inlineStr"/>
+      <c r="D31" s="36" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="12">
+  <mergeCells count="16">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="B3:D3"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A5:D5"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="B8:D8"/>
+    <mergeCell ref="A20:D20"/>
     <mergeCell ref="A7:D7"/>
     <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="B10:D10"/>
+    <mergeCell ref="A18:D18"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="A24:D24"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A14:D14"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9"/>
@@ -1863,152 +1811,133 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D21"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="40" customWidth="1" min="3" max="3"/>
-    <col width="30" customWidth="1" min="4" max="4"/>
-    <col width="25" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="38" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>リリース・ロールバック</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>■ リリース対象一覧</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="28" customHeight="1">
-      <c r="A3" s="7" t="inlineStr">
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="64" t="inlineStr">
+        <is>
+          <t>残対応・懸念・保留</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="63" t="inlineStr">
+        <is>
+          <t>■ 残対応・懸念事項一覧</t>
+        </is>
+      </c>
+      <c r="B2" s="21" t="n"/>
+      <c r="C2" s="21" t="n"/>
+      <c r="D2" s="21" t="n"/>
+      <c r="E2" s="21" t="n"/>
+      <c r="F2" s="22" t="n"/>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="63" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B3" s="7" t="inlineStr">
+      <c r="B3" s="63" t="inlineStr">
         <is>
           <t>種別</t>
         </is>
       </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>対象</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="n"/>
-    </row>
-    <row r="4" ht="25" customHeight="1">
-      <c r="A4" s="6" t="n"/>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n"/>
-      <c r="D4" s="6" t="n"/>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="9" t="n"/>
-      <c r="B5" s="9" t="n"/>
-      <c r="C5" s="9" t="n"/>
-      <c r="D5" s="9" t="n"/>
-    </row>
-    <row r="6" ht="8" customHeight="1"/>
-    <row r="7" ht="28" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>■ デプロイ手順</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="28" customHeight="1">
-      <c r="A8" s="11" t="n"/>
-    </row>
-    <row r="9" ht="25" customHeight="1">
-      <c r="A9" s="11" t="n"/>
-    </row>
-    <row r="10" ht="25" customHeight="1">
-      <c r="A10" s="11" t="n"/>
-    </row>
-    <row r="11" ht="25" customHeight="1">
-      <c r="A11" s="11" t="n"/>
-    </row>
-    <row r="12" ht="25" customHeight="1"/>
-    <row r="13" ht="8" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>■ 注意事項・リスク</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="28" customHeight="1">
-      <c r="A14" s="11" t="n"/>
-    </row>
-    <row r="15" ht="25" customHeight="1">
-      <c r="A15" s="11" t="n"/>
-    </row>
-    <row r="16" ht="25" customHeight="1"/>
-    <row r="17" ht="25" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>■ ロールバック手順</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="25" customHeight="1">
-      <c r="A18" s="11" t="n"/>
-    </row>
-    <row r="19" ht="8" customHeight="1">
-      <c r="A19" s="20" t="n"/>
-    </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="11" t="n"/>
-    </row>
-    <row r="21" ht="28" customHeight="1">
-      <c r="A21" s="11" t="n"/>
-    </row>
-    <row r="22" ht="6" customHeight="1"/>
-    <row r="23" ht="20" customHeight="1"/>
-    <row r="24" ht="18" customHeight="1"/>
-    <row r="25" ht="28" customHeight="1"/>
-    <row r="26" ht="28" customHeight="1"/>
-    <row r="27" ht="28" customHeight="1"/>
-    <row r="28" ht="35" customHeight="1"/>
-    <row r="29" ht="35" customHeight="1"/>
-    <row r="30" ht="8" customHeight="1"/>
-    <row r="31" ht="28" customHeight="1"/>
-    <row r="32" ht="25" customHeight="1"/>
-    <row r="33" ht="25" customHeight="1"/>
-    <row r="34" ht="25" customHeight="1"/>
-    <row r="35" ht="25" customHeight="1"/>
-    <row r="36" ht="8" customHeight="1"/>
-    <row r="37" ht="28" customHeight="1"/>
-    <row r="38" ht="28" customHeight="1"/>
-    <row r="39" ht="25" customHeight="1"/>
+      <c r="C3" s="63" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="D3" s="63" t="inlineStr">
+        <is>
+          <t>関連</t>
+        </is>
+      </c>
+      <c r="E3" s="63" t="inlineStr">
+        <is>
+          <t>ステータス</t>
+        </is>
+      </c>
+      <c r="F3" s="63" t="inlineStr">
+        <is>
+          <t>次アクション</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="40" customHeight="1">
+      <c r="A4" s="29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B4" s="29" t="inlineStr">
+        <is>
+          <t>懸念</t>
+        </is>
+      </c>
+      <c r="C4" s="29" t="inlineStr"/>
+      <c r="D4" s="29" t="inlineStr"/>
+      <c r="E4" s="29" t="inlineStr">
+        <is>
+          <t>未対応</t>
+        </is>
+      </c>
+      <c r="F4" s="29" t="inlineStr"/>
+    </row>
+    <row r="5" ht="40" customHeight="1">
+      <c r="A5" s="29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B5" s="29" t="inlineStr">
+        <is>
+          <t>許容した影響</t>
+        </is>
+      </c>
+      <c r="C5" s="29" t="inlineStr"/>
+      <c r="D5" s="29" t="inlineStr"/>
+      <c r="E5" s="29" t="inlineStr">
+        <is>
+          <t>許容済</t>
+        </is>
+      </c>
+      <c r="F5" s="29" t="inlineStr"/>
+    </row>
+    <row r="6" ht="40" customHeight="1">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B6" s="29" t="inlineStr">
+        <is>
+          <t>後回しの残対応</t>
+        </is>
+      </c>
+      <c r="C6" s="29" t="inlineStr"/>
+      <c r="D6" s="29" t="inlineStr"/>
+      <c r="E6" s="29" t="inlineStr">
+        <is>
+          <t>保留</t>
+        </is>
+      </c>
+      <c r="F6" s="29" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="15">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A17:D17"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A21:D21"/>
-    <mergeCell ref="A15:D15"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="A11:D11"/>
-    <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A10:D10"/>
-    <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A14:D14"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A1:F1"/>
   </mergeCells>
-  <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="landscape" paperSize="9"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
+++ b/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="13">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -82,6 +82,18 @@
       <name val="游ゴシック"/>
       <b val="1"/>
       <sz val="12"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <i val="1"/>
+      <color rgb="FF808080"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="15">
@@ -159,7 +171,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="16">
+  <borders count="21">
     <border>
       <left/>
       <right/>
@@ -298,11 +310,60 @@
         <color rgb="00B4C6E7"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B4C6E7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B4C6E7"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="00B4C6E7"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00B4C6E7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00B4C6E7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00B4C6E7"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color rgb="00B4C6E7"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="75">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -458,6 +519,22 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1293,12 +1370,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-    <col width="28" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="70" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="20" customWidth="1" min="5" max="5"/>
   </cols>
@@ -1311,7 +1388,7 @@
       </c>
     </row>
     <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+      <c r="A2" s="65" t="inlineStr">
         <is>
           <t>■ 影響範囲テーブル</t>
         </is>
@@ -1325,15 +1402,10 @@
       </c>
       <c r="B3" s="62" t="inlineStr">
         <is>
-          <t>種別</t>
+          <t>対象</t>
         </is>
       </c>
       <c r="C3" s="62" t="inlineStr">
-        <is>
-          <t>対象</t>
-        </is>
-      </c>
-      <c r="D3" s="62" t="inlineStr">
         <is>
           <t>問題ない根拠・対応内容</t>
         </is>
@@ -1343,37 +1415,31 @@
       <c r="A4" s="6" t="n"/>
       <c r="B4" s="6" t="n"/>
       <c r="C4" s="6" t="n"/>
-      <c r="D4" s="6" t="n"/>
     </row>
     <row r="5" ht="55" customHeight="1">
       <c r="A5" s="9" t="n"/>
       <c r="B5" s="9" t="n"/>
       <c r="C5" s="9" t="n"/>
-      <c r="D5" s="9" t="n"/>
     </row>
     <row r="6" ht="55" customHeight="1">
       <c r="A6" s="6" t="n"/>
       <c r="B6" s="6" t="n"/>
       <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
     </row>
     <row r="7" ht="55" customHeight="1">
       <c r="A7" s="9" t="n"/>
       <c r="B7" s="9" t="n"/>
       <c r="C7" s="9" t="n"/>
-      <c r="D7" s="9" t="n"/>
     </row>
     <row r="8" ht="55" customHeight="1">
       <c r="A8" s="6" t="n"/>
       <c r="B8" s="6" t="n"/>
       <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
     </row>
     <row r="9" ht="8" customHeight="1">
       <c r="A9" s="9" t="n"/>
       <c r="B9" s="9" t="n"/>
       <c r="C9" s="9" t="n"/>
-      <c r="D9" s="9" t="n"/>
     </row>
     <row r="10" ht="28" customHeight="1"/>
     <row r="11" ht="28" customHeight="1"/>
@@ -1400,6 +1466,9 @@
     <row r="32" ht="40" customHeight="1"/>
     <row r="33" ht="40" customHeight="1"/>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:C2"/>
+  </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9"/>
 </worksheet>
@@ -1411,7 +1480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1438,23 +1507,21 @@
       <c r="C2" s="21" t="n"/>
       <c r="D2" s="22" t="n"/>
     </row>
-    <row r="3" ht="40" customHeight="1">
+    <row r="3" ht="80" customHeight="1">
       <c r="A3" s="29" t="inlineStr"/>
-      <c r="B3" s="21" t="n"/>
-      <c r="C3" s="21" t="n"/>
-      <c r="D3" s="22" t="n"/>
+      <c r="B3" s="66" t="n"/>
+      <c r="C3" s="66" t="n"/>
+      <c r="D3" s="67" t="n"/>
     </row>
     <row r="4" ht="40" customHeight="1">
-      <c r="A4" s="29" t="inlineStr"/>
-      <c r="B4" s="21" t="n"/>
-      <c r="C4" s="21" t="n"/>
-      <c r="D4" s="22" t="n"/>
+      <c r="A4" s="68" t="n"/>
+      <c r="D4" s="69" t="n"/>
     </row>
     <row r="5" ht="40" customHeight="1">
-      <c r="A5" s="29" t="inlineStr"/>
-      <c r="B5" s="21" t="n"/>
-      <c r="C5" s="21" t="n"/>
-      <c r="D5" s="22" t="n"/>
+      <c r="A5" s="70" t="n"/>
+      <c r="B5" s="71" t="n"/>
+      <c r="C5" s="71" t="n"/>
+      <c r="D5" s="72" t="n"/>
     </row>
     <row r="6" ht="6" customHeight="1"/>
     <row r="7" ht="28" customHeight="1">
@@ -1563,65 +1630,13 @@
       <c r="A22" s="19" t="inlineStr"/>
     </row>
     <row r="23" ht="25" customHeight="1"/>
-    <row r="24" ht="25" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>■ 影響確認チェックリスト</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="25" customHeight="1">
-      <c r="A25" s="7" t="n"/>
-      <c r="B25" s="7" t="inlineStr">
-        <is>
-          <t>確認内容</t>
-        </is>
-      </c>
-      <c r="C25" s="7" t="n"/>
-      <c r="D25" s="7" t="n"/>
-    </row>
-    <row r="26" ht="25" customHeight="1">
-      <c r="A26" s="35" t="n"/>
-      <c r="B26" s="36" t="n"/>
-      <c r="C26" s="35" t="inlineStr"/>
-      <c r="D26" s="36" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="35" t="n"/>
-      <c r="B27" s="36" t="n"/>
-      <c r="C27" s="35" t="inlineStr"/>
-      <c r="D27" s="36" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="35" t="n"/>
-      <c r="B28" s="36" t="n"/>
-      <c r="C28" s="35" t="inlineStr"/>
-      <c r="D28" s="36" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" s="35" t="n"/>
-      <c r="B29" s="36" t="n"/>
-      <c r="C29" s="35" t="inlineStr"/>
-      <c r="D29" s="36" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" s="35" t="n"/>
-      <c r="B30" s="36" t="n"/>
-      <c r="C30" s="35" t="inlineStr"/>
-      <c r="D30" s="36" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="35" t="n"/>
-      <c r="B31" s="36" t="n"/>
-      <c r="C31" s="35" t="inlineStr"/>
-      <c r="D31" s="36" t="inlineStr"/>
-    </row>
+    <row r="24" ht="25" customHeight="1"/>
+    <row r="25" ht="25" customHeight="1"/>
+    <row r="26" ht="25" customHeight="1"/>
   </sheetData>
-  <mergeCells count="16">
+  <mergeCells count="13">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A5:D5"/>
     <mergeCell ref="A22:D22"/>
-    <mergeCell ref="A4:D4"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="A20:D20"/>
     <mergeCell ref="A7:D7"/>
@@ -1629,10 +1644,9 @@
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="A18:D18"/>
     <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A3:D3"/>
+    <mergeCell ref="A3:D5"/>
     <mergeCell ref="A21:D21"/>
     <mergeCell ref="B9:D9"/>
-    <mergeCell ref="A24:D24"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -1646,7 +1660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1662,7 +1676,7 @@
     <row r="1" ht="38" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>テスト・検証記録</t>
+          <t>テスト・検証</t>
         </is>
       </c>
     </row>
@@ -1721,83 +1735,91 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="45" customHeight="1">
-      <c r="A7" s="6" t="n"/>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
-      <c r="E7" s="6" t="n"/>
-      <c r="F7" s="6" t="inlineStr"/>
-      <c r="G7" s="6" t="inlineStr"/>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="73" t="inlineStr">
+        <is>
+          <t>※ 区分=実装前 の F/G 列は Phase 3.5（validator）で事前記入済み。区分=実装後 の F/G 列（実際の結果・判定）のみ Phase 5（tester）がテスト実施後に記入する。</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="45" customHeight="1">
-      <c r="A8" s="9" t="n"/>
-      <c r="B8" s="9" t="n"/>
-      <c r="C8" s="9" t="n"/>
-      <c r="D8" s="9" t="n"/>
-      <c r="E8" s="9" t="n"/>
-      <c r="F8" s="9" t="inlineStr"/>
-      <c r="G8" s="9" t="inlineStr"/>
+      <c r="A8" s="6" t="n"/>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="inlineStr"/>
+      <c r="G8" s="6" t="inlineStr"/>
     </row>
     <row r="9" ht="45" customHeight="1">
-      <c r="A9" s="6" t="n"/>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="inlineStr"/>
-      <c r="G9" s="6" t="inlineStr"/>
+      <c r="A9" s="9" t="n"/>
+      <c r="B9" s="9" t="n"/>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="9" t="n"/>
+      <c r="F9" s="9" t="inlineStr"/>
+      <c r="G9" s="9" t="inlineStr"/>
     </row>
     <row r="10" ht="45" customHeight="1">
-      <c r="A10" s="9" t="n"/>
-      <c r="B10" s="9" t="n"/>
-      <c r="C10" s="9" t="n"/>
-      <c r="D10" s="9" t="n"/>
-      <c r="E10" s="9" t="n"/>
-      <c r="F10" s="9" t="inlineStr"/>
-      <c r="G10" s="9" t="inlineStr"/>
+      <c r="A10" s="6" t="n"/>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="inlineStr"/>
+      <c r="G10" s="6" t="inlineStr"/>
     </row>
     <row r="11" ht="45" customHeight="1">
-      <c r="A11" s="6" t="n"/>
-      <c r="B11" s="6" t="n"/>
-      <c r="C11" s="6" t="n"/>
-      <c r="D11" s="6" t="n"/>
-      <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="inlineStr"/>
-      <c r="G11" s="6" t="inlineStr"/>
+      <c r="A11" s="9" t="n"/>
+      <c r="B11" s="9" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="9" t="n"/>
+      <c r="E11" s="9" t="n"/>
+      <c r="F11" s="9" t="inlineStr"/>
+      <c r="G11" s="9" t="inlineStr"/>
     </row>
     <row r="12" ht="45" customHeight="1">
-      <c r="A12" s="9" t="n"/>
-      <c r="B12" s="9" t="n"/>
-      <c r="C12" s="9" t="n"/>
-      <c r="D12" s="9" t="n"/>
-      <c r="E12" s="9" t="n"/>
-      <c r="F12" s="9" t="inlineStr"/>
-      <c r="G12" s="9" t="inlineStr"/>
+      <c r="A12" s="6" t="n"/>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="inlineStr"/>
+      <c r="G12" s="6" t="inlineStr"/>
     </row>
     <row r="13" ht="45" customHeight="1">
-      <c r="A13" s="6" t="n"/>
-      <c r="B13" s="6" t="n"/>
-      <c r="C13" s="6" t="n"/>
-      <c r="D13" s="6" t="n"/>
-      <c r="E13" s="6" t="n"/>
-      <c r="F13" s="6" t="inlineStr"/>
-      <c r="G13" s="6" t="inlineStr"/>
+      <c r="A13" s="9" t="n"/>
+      <c r="B13" s="9" t="n"/>
+      <c r="C13" s="9" t="n"/>
+      <c r="D13" s="9" t="n"/>
+      <c r="E13" s="9" t="n"/>
+      <c r="F13" s="9" t="inlineStr"/>
+      <c r="G13" s="9" t="inlineStr"/>
     </row>
     <row r="14" ht="45" customHeight="1">
-      <c r="A14" s="9" t="n"/>
-      <c r="B14" s="9" t="n"/>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="9" t="n"/>
-      <c r="E14" s="9" t="n"/>
-      <c r="F14" s="9" t="inlineStr"/>
-      <c r="G14" s="9" t="inlineStr"/>
+      <c r="A14" s="6" t="n"/>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="inlineStr"/>
+      <c r="G14" s="6" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="9" t="n"/>
+      <c r="B15" s="9" t="n"/>
+      <c r="C15" s="9" t="n"/>
+      <c r="D15" s="9" t="n"/>
+      <c r="E15" s="9" t="n"/>
+      <c r="F15" s="9" t="inlineStr"/>
+      <c r="G15" s="9" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
+    <mergeCell ref="A1:G1"/>
     <mergeCell ref="A3:G3"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A7:G7"/>
     <mergeCell ref="A5:G5"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -1811,26 +1833,26 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="50" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="30" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="64" t="inlineStr">
+      <c r="A1" s="74" t="inlineStr">
         <is>
           <t>残対応・懸念・保留</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="63" t="inlineStr">
+      <c r="A2" s="65" t="inlineStr">
         <is>
           <t>■ 残対応・懸念事項一覧</t>
         </is>
@@ -1838,36 +1860,30 @@
       <c r="B2" s="21" t="n"/>
       <c r="C2" s="21" t="n"/>
       <c r="D2" s="21" t="n"/>
-      <c r="E2" s="21" t="n"/>
-      <c r="F2" s="22" t="n"/>
+      <c r="E2" s="22" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="63" t="inlineStr">
+      <c r="A3" s="62" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B3" s="63" t="inlineStr">
+      <c r="B3" s="62" t="inlineStr">
         <is>
           <t>種別</t>
         </is>
       </c>
-      <c r="C3" s="63" t="inlineStr">
+      <c r="C3" s="62" t="inlineStr">
         <is>
           <t>内容</t>
         </is>
       </c>
-      <c r="D3" s="63" t="inlineStr">
-        <is>
-          <t>関連</t>
-        </is>
-      </c>
-      <c r="E3" s="63" t="inlineStr">
+      <c r="D3" s="62" t="inlineStr">
         <is>
           <t>ステータス</t>
         </is>
       </c>
-      <c r="F3" s="63" t="inlineStr">
+      <c r="E3" s="62" t="inlineStr">
         <is>
           <t>次アクション</t>
         </is>
@@ -1885,13 +1901,12 @@
         </is>
       </c>
       <c r="C4" s="29" t="inlineStr"/>
-      <c r="D4" s="29" t="inlineStr"/>
-      <c r="E4" s="29" t="inlineStr">
+      <c r="D4" s="29" t="inlineStr">
         <is>
           <t>未対応</t>
         </is>
       </c>
-      <c r="F4" s="29" t="inlineStr"/>
+      <c r="E4" s="29" t="inlineStr"/>
     </row>
     <row r="5" ht="40" customHeight="1">
       <c r="A5" s="29" t="inlineStr">
@@ -1905,13 +1920,12 @@
         </is>
       </c>
       <c r="C5" s="29" t="inlineStr"/>
-      <c r="D5" s="29" t="inlineStr"/>
-      <c r="E5" s="29" t="inlineStr">
+      <c r="D5" s="29" t="inlineStr">
         <is>
           <t>許容済</t>
         </is>
       </c>
-      <c r="F5" s="29" t="inlineStr"/>
+      <c r="E5" s="29" t="inlineStr"/>
     </row>
     <row r="6" ht="40" customHeight="1">
       <c r="A6" s="29" t="inlineStr">
@@ -1925,18 +1939,19 @@
         </is>
       </c>
       <c r="C6" s="29" t="inlineStr"/>
-      <c r="D6" s="29" t="inlineStr"/>
-      <c r="E6" s="29" t="inlineStr">
+      <c r="D6" s="29" t="inlineStr">
         <is>
           <t>保留</t>
         </is>
       </c>
-      <c r="F6" s="29" t="inlineStr"/>
-    </row>
+      <c r="E6" s="29" t="inlineStr"/>
+    </row>
+    <row r="7"/>
+    <row r="8"/>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
+++ b/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
@@ -1207,7 +1207,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -1294,11 +1294,9 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="n"/>
-      <c r="B11" s="22" t="n"/>
-      <c r="C11" s="21" t="n"/>
-      <c r="D11" s="21" t="n"/>
-      <c r="E11" s="22" t="n"/>
+      <c r="A11" s="35" t="n"/>
+      <c r="B11" s="35" t="inlineStr"/>
+      <c r="C11" s="36" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="35" t="n"/>
@@ -1315,27 +1313,24 @@
       <c r="B14" s="35" t="inlineStr"/>
       <c r="C14" s="36" t="inlineStr"/>
     </row>
-    <row r="15">
-      <c r="A15" s="35" t="n"/>
-      <c r="B15" s="35" t="inlineStr"/>
-      <c r="C15" s="36" t="inlineStr"/>
+    <row r="15"/>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>■ 懸念事項</t>
+        </is>
+      </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>■ 懸念事項</t>
-        </is>
-      </c>
+      <c r="A17" s="11" t="n"/>
     </row>
     <row r="18">
-      <c r="A18" s="11" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="17" t="n"/>
-    </row>
-    <row r="20" ht="28" customHeight="1">
-      <c r="A20" s="11" t="n"/>
-    </row>
+      <c r="A18" s="17" t="n"/>
+    </row>
+    <row r="19" ht="28" customHeight="1">
+      <c r="A19" s="11" t="n"/>
+    </row>
+    <row r="20" ht="28" customHeight="1"/>
     <row r="21" ht="28" customHeight="1"/>
     <row r="22" ht="25" customHeight="1"/>
     <row r="23" ht="25" customHeight="1"/>
@@ -1347,17 +1342,16 @@
     <row r="29" ht="35" customHeight="1"/>
     <row r="30" ht="35" customHeight="1"/>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="A20:E20"/>
+  <mergeCells count="9">
+    <mergeCell ref="A18:E18"/>
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A16:E16"/>
+    <mergeCell ref="A7:E7"/>
     <mergeCell ref="A10:E10"/>
-    <mergeCell ref="A7:E7"/>
     <mergeCell ref="A19:E19"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="B11:E11"/>
     <mergeCell ref="A8:E8"/>
     <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A18:E18"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9"/>
@@ -1393,6 +1387,8 @@
           <t>■ 影響範囲テーブル</t>
         </is>
       </c>
+      <c r="B2" s="21" t="n"/>
+      <c r="C2" s="22" t="n"/>
     </row>
     <row r="3" ht="28" customHeight="1">
       <c r="A3" s="62" t="inlineStr">
@@ -1466,7 +1462,8 @@
     <row r="32" ht="40" customHeight="1"/>
     <row r="33" ht="40" customHeight="1"/>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A1:C1"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -1480,7 +1477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1635,18 +1632,18 @@
     <row r="26" ht="25" customHeight="1"/>
   </sheetData>
   <mergeCells count="13">
+    <mergeCell ref="B10:D10"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A18:D18"/>
     <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A12:D12"/>
     <mergeCell ref="B8:D8"/>
     <mergeCell ref="A20:D20"/>
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="A19:D19"/>
-    <mergeCell ref="B10:D10"/>
-    <mergeCell ref="A18:D18"/>
-    <mergeCell ref="A12:D12"/>
     <mergeCell ref="A3:D5"/>
     <mergeCell ref="A21:D21"/>
     <mergeCell ref="B9:D9"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A19:D19"/>
     <mergeCell ref="A2:D2"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -1833,7 +1830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1946,8 +1943,6 @@
       </c>
       <c r="E6" s="29" t="inlineStr"/>
     </row>
-    <row r="7"/>
-    <row r="8"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A2:E2"/>

--- a/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
+++ b/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
@@ -1313,7 +1313,6 @@
       <c r="B14" s="35" t="inlineStr"/>
       <c r="C14" s="36" t="inlineStr"/>
     </row>
-    <row r="15"/>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
@@ -1343,7 +1342,6 @@
     <row r="30" ht="35" customHeight="1"/>
   </sheetData>
   <mergeCells count="9">
-    <mergeCell ref="A18:E18"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A16:E16"/>
     <mergeCell ref="A7:E7"/>
@@ -1352,6 +1350,7 @@
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A8:E8"/>
     <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A18:E18"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9"/>
@@ -1657,12 +1656,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
     <col width="35" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
@@ -1708,25 +1708,30 @@
       </c>
       <c r="C6" s="7" t="inlineStr">
         <is>
+          <t>実行種別</t>
+        </is>
+      </c>
+      <c r="D6" s="7" t="inlineStr">
+        <is>
           <t>テスト項目</t>
         </is>
       </c>
-      <c r="D6" s="7" t="inlineStr">
+      <c r="E6" s="7" t="inlineStr">
         <is>
           <t>確認方法</t>
         </is>
       </c>
-      <c r="E6" s="7" t="inlineStr">
+      <c r="F6" s="7" t="inlineStr">
         <is>
           <t>期待結果</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>実際の結果</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>判定</t>
         </is>
@@ -1742,82 +1747,82 @@
     <row r="8" ht="45" customHeight="1">
       <c r="A8" s="6" t="n"/>
       <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="inlineStr"/>
+      <c r="F8" s="6" t="n"/>
       <c r="G8" s="6" t="inlineStr"/>
+      <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9" ht="45" customHeight="1">
       <c r="A9" s="9" t="n"/>
       <c r="B9" s="9" t="n"/>
-      <c r="C9" s="9" t="n"/>
       <c r="D9" s="9" t="n"/>
       <c r="E9" s="9" t="n"/>
-      <c r="F9" s="9" t="inlineStr"/>
+      <c r="F9" s="9" t="n"/>
       <c r="G9" s="9" t="inlineStr"/>
+      <c r="H9" s="9" t="inlineStr"/>
     </row>
     <row r="10" ht="45" customHeight="1">
       <c r="A10" s="6" t="n"/>
       <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="inlineStr"/>
+      <c r="F10" s="6" t="n"/>
       <c r="G10" s="6" t="inlineStr"/>
+      <c r="H10" s="6" t="inlineStr"/>
     </row>
     <row r="11" ht="45" customHeight="1">
       <c r="A11" s="9" t="n"/>
       <c r="B11" s="9" t="n"/>
-      <c r="C11" s="9" t="n"/>
       <c r="D11" s="9" t="n"/>
       <c r="E11" s="9" t="n"/>
-      <c r="F11" s="9" t="inlineStr"/>
+      <c r="F11" s="9" t="n"/>
       <c r="G11" s="9" t="inlineStr"/>
+      <c r="H11" s="9" t="inlineStr"/>
     </row>
     <row r="12" ht="45" customHeight="1">
       <c r="A12" s="6" t="n"/>
       <c r="B12" s="6" t="n"/>
-      <c r="C12" s="6" t="n"/>
       <c r="D12" s="6" t="n"/>
       <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="inlineStr"/>
+      <c r="F12" s="6" t="n"/>
       <c r="G12" s="6" t="inlineStr"/>
+      <c r="H12" s="6" t="inlineStr"/>
     </row>
     <row r="13" ht="45" customHeight="1">
       <c r="A13" s="9" t="n"/>
       <c r="B13" s="9" t="n"/>
-      <c r="C13" s="9" t="n"/>
       <c r="D13" s="9" t="n"/>
       <c r="E13" s="9" t="n"/>
-      <c r="F13" s="9" t="inlineStr"/>
+      <c r="F13" s="9" t="n"/>
       <c r="G13" s="9" t="inlineStr"/>
+      <c r="H13" s="9" t="inlineStr"/>
     </row>
     <row r="14" ht="45" customHeight="1">
       <c r="A14" s="6" t="n"/>
       <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="n"/>
       <c r="D14" s="6" t="n"/>
       <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="inlineStr"/>
+      <c r="F14" s="6" t="n"/>
       <c r="G14" s="6" t="inlineStr"/>
+      <c r="H14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="9" t="n"/>
       <c r="B15" s="9" t="n"/>
-      <c r="C15" s="9" t="n"/>
       <c r="D15" s="9" t="n"/>
       <c r="E15" s="9" t="n"/>
-      <c r="F15" s="9" t="inlineStr"/>
+      <c r="F15" s="9" t="n"/>
       <c r="G15" s="9" t="inlineStr"/>
+      <c r="H15" s="9" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A3:G3"/>
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A7:G7"/>
-    <mergeCell ref="A5:G5"/>
+    <mergeCell ref="A3:H3"/>
+    <mergeCell ref="A5:H5"/>
+    <mergeCell ref="A7:H7"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A1:H1"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9"/>

--- a/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
+++ b/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
@@ -1661,7 +1661,6 @@
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="35" customWidth="1" min="4" max="4"/>
     <col width="30" customWidth="1" min="5" max="5"/>
@@ -1740,7 +1739,7 @@
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="73" t="inlineStr">
         <is>
-          <t>※ 区分=実装前 の F/G 列は Phase 3.5（validator）で事前記入済み。区分=実装後 の F/G 列（実際の結果・判定）のみ Phase 5（tester）がテスト実施後に記入する。</t>
+          <t>※ 区分=実装前 の G/H 列は Phase 3.5（validator）で事前記入済み。区分=実装後 の G/H 列（実際の結果・判定）のみ Phase 5（tester）がテスト実施後に記入する。</t>
         </is>
       </c>
     </row>

--- a/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
+++ b/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="13">
+  <fonts count="15">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -94,6 +94,16 @@
       <i val="1"/>
       <color rgb="FF808080"/>
       <sz val="9"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <sz val="11"/>
     </font>
   </fonts>
   <fills count="15">
@@ -363,7 +373,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="77">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -537,6 +547,10 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1663,9 +1677,9 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="30" customWidth="1" min="5" max="5"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
     <col width="30" customWidth="1" min="6" max="6"/>
-    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="7" max="7"/>
     <col width="30" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
@@ -1705,7 +1719,7 @@
           <t>区分</t>
         </is>
       </c>
-      <c r="C6" s="7" t="inlineStr">
+      <c r="C6" s="75" t="inlineStr">
         <is>
           <t>実行種別</t>
         </is>
@@ -1720,108 +1734,121 @@
           <t>確認方法</t>
         </is>
       </c>
-      <c r="F6" s="7" t="inlineStr">
+      <c r="F6" s="22" t="n"/>
+      <c r="G6" s="7" t="inlineStr">
         <is>
           <t>期待結果</t>
         </is>
       </c>
-      <c r="G6" s="7" t="inlineStr">
+      <c r="H6" s="7" t="inlineStr">
         <is>
           <t>実際の結果</t>
-        </is>
-      </c>
-      <c r="H6" s="7" t="inlineStr">
-        <is>
-          <t>判定</t>
         </is>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="73" t="inlineStr">
         <is>
-          <t>※ 区分=実装前 の G/H 列は Phase 3.5（validator）で事前記入済み。区分=実装後 の G/H 列（実際の結果・判定）のみ Phase 5（tester）がテスト実施後に記入する。</t>
+          <t>※ 区分=実装前 の H 列（実際の結果）は Phase 3.5（validator）が記入。実装後行は Phase 5（tester）が記入。値は「OK」または「NG: &lt;理由&gt;」で始めること（空欄禁止）。</t>
         </is>
       </c>
     </row>
     <row r="8" ht="45" customHeight="1">
       <c r="A8" s="6" t="n"/>
       <c r="B8" s="6" t="n"/>
+      <c r="C8" s="76" t="n"/>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n"/>
-      <c r="F8" s="6" t="n"/>
+      <c r="F8" s="22" t="n"/>
       <c r="G8" s="6" t="inlineStr"/>
       <c r="H8" s="6" t="inlineStr"/>
     </row>
     <row r="9" ht="45" customHeight="1">
       <c r="A9" s="9" t="n"/>
       <c r="B9" s="9" t="n"/>
+      <c r="C9" s="76" t="n"/>
       <c r="D9" s="9" t="n"/>
       <c r="E9" s="9" t="n"/>
-      <c r="F9" s="9" t="n"/>
+      <c r="F9" s="22" t="n"/>
       <c r="G9" s="9" t="inlineStr"/>
       <c r="H9" s="9" t="inlineStr"/>
     </row>
     <row r="10" ht="45" customHeight="1">
       <c r="A10" s="6" t="n"/>
       <c r="B10" s="6" t="n"/>
+      <c r="C10" s="76" t="n"/>
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
+      <c r="F10" s="22" t="n"/>
       <c r="G10" s="6" t="inlineStr"/>
       <c r="H10" s="6" t="inlineStr"/>
     </row>
     <row r="11" ht="45" customHeight="1">
       <c r="A11" s="9" t="n"/>
       <c r="B11" s="9" t="n"/>
+      <c r="C11" s="76" t="n"/>
       <c r="D11" s="9" t="n"/>
       <c r="E11" s="9" t="n"/>
-      <c r="F11" s="9" t="n"/>
+      <c r="F11" s="22" t="n"/>
       <c r="G11" s="9" t="inlineStr"/>
       <c r="H11" s="9" t="inlineStr"/>
     </row>
     <row r="12" ht="45" customHeight="1">
       <c r="A12" s="6" t="n"/>
       <c r="B12" s="6" t="n"/>
+      <c r="C12" s="76" t="n"/>
       <c r="D12" s="6" t="n"/>
       <c r="E12" s="6" t="n"/>
-      <c r="F12" s="6" t="n"/>
+      <c r="F12" s="22" t="n"/>
       <c r="G12" s="6" t="inlineStr"/>
       <c r="H12" s="6" t="inlineStr"/>
     </row>
     <row r="13" ht="45" customHeight="1">
       <c r="A13" s="9" t="n"/>
       <c r="B13" s="9" t="n"/>
+      <c r="C13" s="76" t="n"/>
       <c r="D13" s="9" t="n"/>
       <c r="E13" s="9" t="n"/>
-      <c r="F13" s="9" t="n"/>
+      <c r="F13" s="22" t="n"/>
       <c r="G13" s="9" t="inlineStr"/>
       <c r="H13" s="9" t="inlineStr"/>
     </row>
     <row r="14" ht="45" customHeight="1">
       <c r="A14" s="6" t="n"/>
       <c r="B14" s="6" t="n"/>
+      <c r="C14" s="76" t="n"/>
       <c r="D14" s="6" t="n"/>
       <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
+      <c r="F14" s="22" t="n"/>
       <c r="G14" s="6" t="inlineStr"/>
       <c r="H14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="9" t="n"/>
       <c r="B15" s="9" t="n"/>
+      <c r="C15" s="76" t="n"/>
       <c r="D15" s="9" t="n"/>
       <c r="E15" s="9" t="n"/>
-      <c r="F15" s="9" t="n"/>
+      <c r="F15" s="22" t="n"/>
       <c r="G15" s="9" t="inlineStr"/>
       <c r="H15" s="9" t="inlineStr"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="14">
+    <mergeCell ref="E12:F12"/>
     <mergeCell ref="A3:H3"/>
+    <mergeCell ref="E6:F6"/>
     <mergeCell ref="A5:H5"/>
     <mergeCell ref="A7:H7"/>
+    <mergeCell ref="E10:F10"/>
+    <mergeCell ref="E15:F15"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="E13:F13"/>
+    <mergeCell ref="E14:F14"/>
     <mergeCell ref="A1:H1"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="E8:F8"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9"/>

--- a/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
+++ b/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -105,6 +105,12 @@
       <name val="游ゴシック"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="游ゴシック"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="15">
     <fill>
@@ -373,7 +379,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -551,6 +557,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -1719,7 +1729,7 @@
           <t>区分</t>
         </is>
       </c>
-      <c r="C6" s="75" t="inlineStr">
+      <c r="C6" s="77" t="inlineStr">
         <is>
           <t>実行種別</t>
         </is>
@@ -1756,7 +1766,7 @@
     <row r="8" ht="45" customHeight="1">
       <c r="A8" s="6" t="n"/>
       <c r="B8" s="6" t="n"/>
-      <c r="C8" s="76" t="n"/>
+      <c r="C8" s="78" t="n"/>
       <c r="D8" s="6" t="n"/>
       <c r="E8" s="6" t="n"/>
       <c r="F8" s="22" t="n"/>
@@ -1766,7 +1776,7 @@
     <row r="9" ht="45" customHeight="1">
       <c r="A9" s="9" t="n"/>
       <c r="B9" s="9" t="n"/>
-      <c r="C9" s="76" t="n"/>
+      <c r="C9" s="78" t="n"/>
       <c r="D9" s="9" t="n"/>
       <c r="E9" s="9" t="n"/>
       <c r="F9" s="22" t="n"/>
@@ -1776,7 +1786,7 @@
     <row r="10" ht="45" customHeight="1">
       <c r="A10" s="6" t="n"/>
       <c r="B10" s="6" t="n"/>
-      <c r="C10" s="76" t="n"/>
+      <c r="C10" s="78" t="n"/>
       <c r="D10" s="6" t="n"/>
       <c r="E10" s="6" t="n"/>
       <c r="F10" s="22" t="n"/>
@@ -1786,7 +1796,7 @@
     <row r="11" ht="45" customHeight="1">
       <c r="A11" s="9" t="n"/>
       <c r="B11" s="9" t="n"/>
-      <c r="C11" s="76" t="n"/>
+      <c r="C11" s="78" t="n"/>
       <c r="D11" s="9" t="n"/>
       <c r="E11" s="9" t="n"/>
       <c r="F11" s="22" t="n"/>
@@ -1796,7 +1806,7 @@
     <row r="12" ht="45" customHeight="1">
       <c r="A12" s="6" t="n"/>
       <c r="B12" s="6" t="n"/>
-      <c r="C12" s="76" t="n"/>
+      <c r="C12" s="78" t="n"/>
       <c r="D12" s="6" t="n"/>
       <c r="E12" s="6" t="n"/>
       <c r="F12" s="22" t="n"/>
@@ -1806,7 +1816,7 @@
     <row r="13" ht="45" customHeight="1">
       <c r="A13" s="9" t="n"/>
       <c r="B13" s="9" t="n"/>
-      <c r="C13" s="76" t="n"/>
+      <c r="C13" s="78" t="n"/>
       <c r="D13" s="9" t="n"/>
       <c r="E13" s="9" t="n"/>
       <c r="F13" s="22" t="n"/>
@@ -1816,7 +1826,7 @@
     <row r="14" ht="45" customHeight="1">
       <c r="A14" s="6" t="n"/>
       <c r="B14" s="6" t="n"/>
-      <c r="C14" s="76" t="n"/>
+      <c r="C14" s="78" t="n"/>
       <c r="D14" s="6" t="n"/>
       <c r="E14" s="6" t="n"/>
       <c r="F14" s="22" t="n"/>
@@ -1826,7 +1836,7 @@
     <row r="15">
       <c r="A15" s="9" t="n"/>
       <c r="B15" s="9" t="n"/>
-      <c r="C15" s="76" t="n"/>
+      <c r="C15" s="78" t="n"/>
       <c r="D15" s="9" t="n"/>
       <c r="E15" s="9" t="n"/>
       <c r="F15" s="22" t="n"/>

--- a/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
+++ b/scripts/python/backlog-xlsx/対応記録テンプレート.xlsx
@@ -723,7 +723,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -820,9 +820,63 @@
     <row r="16" ht="28" customHeight="1">
       <c r="A16" s="6" t="inlineStr"/>
     </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>■ NG対応履歴（/test NG 修正ループ記録）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>回次</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>TC番号</t>
+        </is>
+      </c>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>NG原因</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>修正内容</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="28" customHeight="1">
+      <c r="A20" s="3" t="inlineStr"/>
+      <c r="B20" s="3" t="inlineStr"/>
+      <c r="C20" s="3" t="inlineStr"/>
+      <c r="D20" s="3" t="inlineStr"/>
+    </row>
+    <row r="21" ht="28" customHeight="1">
+      <c r="A21" s="5" t="inlineStr"/>
+      <c r="B21" s="5" t="inlineStr"/>
+      <c r="C21" s="5" t="inlineStr"/>
+      <c r="D21" s="5" t="inlineStr"/>
+    </row>
+    <row r="22" ht="28" customHeight="1">
+      <c r="A22" s="3" t="inlineStr"/>
+      <c r="B22" s="3" t="inlineStr"/>
+      <c r="C22" s="3" t="inlineStr"/>
+      <c r="D22" s="3" t="inlineStr"/>
+    </row>
+    <row r="23" ht="28" customHeight="1">
+      <c r="A23" s="5" t="inlineStr"/>
+      <c r="B23" s="5" t="inlineStr"/>
+      <c r="C23" s="5" t="inlineStr"/>
+      <c r="D23" s="5" t="inlineStr"/>
+    </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A18:D18"/>
     <mergeCell ref="A6:D6"/>
     <mergeCell ref="A2:D5"/>
     <mergeCell ref="A15:D15"/>
